--- a/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_0.xlsx
+++ b/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_0.xlsx
@@ -20,8 +20,10 @@
     <sheet name="algoritmo_A_iteraciones" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="valor_asignado" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="algoritmo_A" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="validacion_snapshot" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="validacion_final" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="puntajes_EA" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="informe_global" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="validacion_snapshot" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="validacion_final" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="algoritmo_A" vbProcedure="false">algoritmo_A!$A$1:$E$15</definedName>
@@ -68,6 +70,39 @@
     <definedName function="false" hidden="false" name="datos_referencia_sd_value" vbProcedure="false">datos_referencia!$E$2</definedName>
     <definedName function="false" hidden="false" name="datos_referencia_u_ref_check" vbProcedure="false">datos_referencia!$G$2</definedName>
     <definedName function="false" hidden="false" name="datos_referencia_x_pt_ref" vbProcedure="false">datos_referencia!$F$2</definedName>
+    <definedName function="false" hidden="false" name="informe_global" vbProcedure="false">informe_global!$A$1:$R$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_bloque" vbProcedure="false">informe_global!$B$2:$B$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_Cuestionable" vbProcedure="false">informe_global!$P$2:$P$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_estado" vbProcedure="false">informe_global!$R$2:$R$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_method" vbProcedure="false">informe_global!$D$2:$D$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_method_key" vbProcedure="false">informe_global!$C$2:$C$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_No_satisfactorio" vbProcedure="false">informe_global!$Q$2:$Q$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_N_A" vbProcedure="false">informe_global!$N$2:$N$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_n_participants" vbProcedure="false">informe_global!$L$2:$L$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_Satisfactorio" vbProcedure="false">informe_global!$O$2:$O$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_score" vbProcedure="false">informe_global!$M$2:$M$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_sigma_pt" vbProcedure="false">informe_global!$F$2:$F$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_tabla" vbProcedure="false">informe_global!$A$2:$A$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_u_hom" vbProcedure="false">informe_global!$H$2:$H$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_u_stab" vbProcedure="false">informe_global!$I$2:$I$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_U_xpt" vbProcedure="false">informe_global!$K$2:$K$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_u_xpt_def" vbProcedure="false">informe_global!$J$2:$J$26</definedName>
+    <definedName function="false" hidden="false" name="informe_global_x_pt" vbProcedure="false">informe_global!$E$2:$E$26</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA" vbProcedure="false">puntajes_EA!$A$1:$N$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_En_score" vbProcedure="false">puntajes_EA!$L$2:$L$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_En_score_eval" vbProcedure="false">puntajes_EA!$M$2:$M$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_estado" vbProcedure="false">puntajes_EA!$N$2:$N$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_method" vbProcedure="false">puntajes_EA!$B$2:$B$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_method_key" vbProcedure="false">puntajes_EA!$A$2:$A$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_participant_id" vbProcedure="false">puntajes_EA!$C$2:$C$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_result" vbProcedure="false">puntajes_EA!$D$2:$D$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_u_xi" vbProcedure="false">puntajes_EA!$E$2:$E$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_zeta_score" vbProcedure="false">puntajes_EA!$J$2:$J$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_zeta_score_eval" vbProcedure="false">puntajes_EA!$K$2:$K$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_z_prime_score" vbProcedure="false">puntajes_EA!$H$2:$H$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_z_prime_score_eval" vbProcedure="false">puntajes_EA!$I$2:$I$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_z_score" vbProcedure="false">puntajes_EA!$F$2:$F$61</definedName>
+    <definedName function="false" hidden="false" name="puntajes_EA_z_score_eval" vbProcedure="false">puntajes_EA!$G$2:$G$61</definedName>
     <definedName function="false" hidden="false" name="readme" vbProcedure="false">README!$A$3:$B$11</definedName>
     <definedName function="false" hidden="false" name="readme_bloque" vbProcedure="false">README!$A$4:$A$11</definedName>
     <definedName function="false" hidden="false" name="readme_contenido" vbProcedure="false">README!$B$4:$B$11</definedName>
@@ -122,14 +157,14 @@
     <definedName function="false" hidden="false" name="snapshot_z_prime_score_eval" vbProcedure="false">validacion_snapshot!$Z$2:$Z$133</definedName>
     <definedName function="false" hidden="false" name="snapshot_z_score" vbProcedure="false">validacion_snapshot!$W$2:$W$133</definedName>
     <definedName function="false" hidden="false" name="snapshot_z_score_eval" vbProcedure="false">validacion_snapshot!$X$2:$X$133</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_errores" vbProcedure="false">validacion_final!$A$19:$C$24</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_errores_conteo" vbProcedure="false">validacion_final!$C$20:$C$24</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_errores_error_excel" vbProcedure="false">validacion_final!$A$20:$A$24</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_errores_etiqueta" vbProcedure="false">validacion_final!$B$20:$B$24</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_resumen" vbProcedure="false">validacion_final!$A$1:$C$14</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_resumen_estado" vbProcedure="false">validacion_final!$B$2:$B$14</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_resumen_hoja" vbProcedure="false">validacion_final!$A$2:$A$14</definedName>
-    <definedName function="false" hidden="false" name="validacion_final_resumen_notas" vbProcedure="false">validacion_final!$C$2:$C$14</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_errores" vbProcedure="false">validacion_final!$A$21:$C$26</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_errores_conteo" vbProcedure="false">validacion_final!$C$22:$C$26</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_errores_error_excel" vbProcedure="false">validacion_final!$A$22:$A$26</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_errores_etiqueta" vbProcedure="false">validacion_final!$B$22:$B$26</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_resumen" vbProcedure="false">validacion_final!$A$1:$C$16</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_resumen_estado" vbProcedure="false">validacion_final!$B$2:$B$16</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_resumen_hoja" vbProcedure="false">validacion_final!$A$2:$A$16</definedName>
+    <definedName function="false" hidden="false" name="validacion_final_resumen_notas" vbProcedure="false">validacion_final!$C$2:$C$16</definedName>
     <definedName function="false" hidden="false" name="valor_asignado" vbProcedure="false">valor_asignado!$A$1:$K$6</definedName>
     <definedName function="false" hidden="false" name="valor_asignado_estado" vbProcedure="false">valor_asignado!$K$2:$K$6</definedName>
     <definedName function="false" hidden="false" name="valor_asignado_method" vbProcedure="false">valor_asignado!$B$2:$B$6</definedName>
@@ -152,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="289">
   <si>
     <t xml:space="preserve">Excel con formulas validacion O3</t>
   </si>
@@ -184,7 +219,7 @@
     <t xml:space="preserve">Fecha de generacion</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-13 18:12:26 -0500</t>
+    <t xml:space="preserve">2026-05-13 18:36:03 -0500</t>
   </si>
   <si>
     <t xml:space="preserve">Script generador</t>
@@ -773,6 +808,75 @@
     <t xml:space="preserve">primera_iteración_3ra_cifra</t>
   </si>
   <si>
+    <t xml:space="preserve">result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_xi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_score_eval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_prime_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_prime_score_eval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeta_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeta_score_eval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En_score_eval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfactorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuestionable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No satisfactorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores asignados e incertidumbre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parámetros por método</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen global de evaluaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conteos por método y categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_prime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En</t>
+  </si>
+  <si>
     <t xml:space="preserve">combo_id</t>
   </si>
   <si>
@@ -782,51 +886,6 @@
     <t xml:space="preserve">section</t>
   </si>
   <si>
-    <t xml:space="preserve">result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_xi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_score_eval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_prime_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_prime_score_eval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeta_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeta_score_eval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En_score_eval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satisfactorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuestionable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No satisfactorio</t>
-  </si>
-  <si>
     <t xml:space="preserve">resultado_homogeneidad</t>
   </si>
   <si>
@@ -881,30 +940,6 @@
     <t xml:space="preserve">informe_global</t>
   </si>
   <si>
-    <t xml:space="preserve">Valores asignados e incertidumbre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parámetros por método</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumen global de evaluaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conteos por método y categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_prime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En</t>
-  </si>
-  <si>
     <t xml:space="preserve">hoja</t>
   </si>
   <si>
@@ -963,6 +998,12 @@
   </si>
   <si>
     <t xml:space="preserve">Resumen visible app.R y comparacion contra snapshot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puntajes z, z', zeta y En por metodo y participante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conteos globales por metodo, score y categoria.</t>
   </si>
   <si>
     <t xml:space="preserve">validacion_snapshot</t>
@@ -8361,6 +8402,4510 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:N61"/>
+  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C2,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C2,datos_participantes!$A:$A,0))</f>
+        <v>5.36666666666667E-006</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D2)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0))=0),"",(D2-INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <f aca="false">IF(F2="","N/A",IF(ABS(F2)&lt;=2,"Satisfactorio",IF(ABS(F2)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D2)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2)=0),"",(D2-INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B2,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <f aca="false">IF(H2="","N/A",IF(ABS(H2)&lt;=2,"Satisfactorio",IF(ABS(H2)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D2)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E2^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2))),SQRT(E2^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2)=0),"",(D2-INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))/SQRT(E2^2+INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <f aca="false">IF(J2="","N/A",IF(ABS(J2)&lt;=2,"Satisfactorio",IF(ABS(J2)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D2)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E2)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0)))^2))),SQRT((2*E2)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0)))^2)=0),"",(D2-INDEX(valor_asignado!$C:$C,MATCH(B2,valor_asignado!$B:$B,0)))/SQRT((2*E2)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B2,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <f aca="false">IF(L2="","N/A",IF(ABS(L2)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D2="",validacion_snapshot!$U$49=""),0,IFERROR(ABS(D2-validacion_snapshot!$U$49),1E+099)),IF(AND(E2="",validacion_snapshot!$V$49=""),0,IFERROR(ABS(E2-validacion_snapshot!$V$49),1E+099)),IF(AND(F2="",validacion_snapshot!$W$49=""),0,IFERROR(ABS(F2-validacion_snapshot!$W$49),1E+099)),IF(AND(H2="",validacion_snapshot!$Y$49=""),0,IFERROR(ABS(H2-validacion_snapshot!$Y$49),1E+099)),IF(AND(J2="",validacion_snapshot!$AA$49=""),0,IFERROR(ABS(J2-validacion_snapshot!$AA$49),1E+099)),IF(AND(L2="",validacion_snapshot!$AC$49=""),0,IFERROR(ABS(L2-validacion_snapshot!$AC$49),1E+099)))&lt;=0.00000001,G2=validacion_snapshot!$X$49,I2=validacion_snapshot!$Z$49,K2=validacion_snapshot!$AB$49,M2=validacion_snapshot!$AD$49),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C3,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C3,datos_participantes!$A:$A,0))</f>
+        <v>1.8475208614068E-006</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0))=0),"",(D3-INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f aca="false">IF(F3="","N/A",IF(ABS(F3)&lt;=2,"Satisfactorio",IF(ABS(F3)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2)=0),"",(D3-INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B3,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <f aca="false">IF(H3="","N/A",IF(ABS(H3)&lt;=2,"Satisfactorio",IF(ABS(H3)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E3^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2))),SQRT(E3^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2)=0),"",(D3-INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))/SQRT(E3^2+INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <f aca="false">IF(J3="","N/A",IF(ABS(J3)&lt;=2,"Satisfactorio",IF(ABS(J3)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E3)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0)))^2))),SQRT((2*E3)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0)))^2)=0),"",(D3-INDEX(valor_asignado!$C:$C,MATCH(B3,valor_asignado!$B:$B,0)))/SQRT((2*E3)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B3,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <f aca="false">IF(L3="","N/A",IF(ABS(L3)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D3="",validacion_snapshot!$U$50=""),0,IFERROR(ABS(D3-validacion_snapshot!$U$50),1E+099)),IF(AND(E3="",validacion_snapshot!$V$50=""),0,IFERROR(ABS(E3-validacion_snapshot!$V$50),1E+099)),IF(AND(F3="",validacion_snapshot!$W$50=""),0,IFERROR(ABS(F3-validacion_snapshot!$W$50),1E+099)),IF(AND(H3="",validacion_snapshot!$Y$50=""),0,IFERROR(ABS(H3-validacion_snapshot!$Y$50),1E+099)),IF(AND(J3="",validacion_snapshot!$AA$50=""),0,IFERROR(ABS(J3-validacion_snapshot!$AA$50),1E+099)),IF(AND(L3="",validacion_snapshot!$AC$50=""),0,IFERROR(ABS(L3-validacion_snapshot!$AC$50),1E+099)))&lt;=0.00000001,G3=validacion_snapshot!$X$50,I3=validacion_snapshot!$Z$50,K3=validacion_snapshot!$AB$50,M3=validacion_snapshot!$AD$50),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C4,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C4,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0))=0),"",(D4-INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <f aca="false">IF(F4="","N/A",IF(ABS(F4)&lt;=2,"Satisfactorio",IF(ABS(F4)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2)=0),"",(D4-INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B4,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <f aca="false">IF(H4="","N/A",IF(ABS(H4)&lt;=2,"Satisfactorio",IF(ABS(H4)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E4^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2))),SQRT(E4^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2)=0),"",(D4-INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))/SQRT(E4^2+INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <f aca="false">IF(J4="","N/A",IF(ABS(J4)&lt;=2,"Satisfactorio",IF(ABS(J4)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E4)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0)))^2))),SQRT((2*E4)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0)))^2)=0),"",(D4-INDEX(valor_asignado!$C:$C,MATCH(B4,valor_asignado!$B:$B,0)))/SQRT((2*E4)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B4,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="str">
+        <f aca="false">IF(L4="","N/A",IF(ABS(L4)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N4" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D4="",validacion_snapshot!$U$51=""),0,IFERROR(ABS(D4-validacion_snapshot!$U$51),1E+099)),IF(AND(E4="",validacion_snapshot!$V$51=""),0,IFERROR(ABS(E4-validacion_snapshot!$V$51),1E+099)),IF(AND(F4="",validacion_snapshot!$W$51=""),0,IFERROR(ABS(F4-validacion_snapshot!$W$51),1E+099)),IF(AND(H4="",validacion_snapshot!$Y$51=""),0,IFERROR(ABS(H4-validacion_snapshot!$Y$51),1E+099)),IF(AND(J4="",validacion_snapshot!$AA$51=""),0,IFERROR(ABS(J4-validacion_snapshot!$AA$51),1E+099)),IF(AND(L4="",validacion_snapshot!$AC$51=""),0,IFERROR(ABS(L4-validacion_snapshot!$AC$51),1E+099)))&lt;=0.00000001,G4=validacion_snapshot!$X$51,I4=validacion_snapshot!$Z$51,K4=validacion_snapshot!$AB$51,M4=validacion_snapshot!$AD$51),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C5,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C5,datos_participantes!$A:$A,0))</f>
+        <v>6.69336321374473E-006</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0))=0),"",(D5-INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f aca="false">IF(F5="","N/A",IF(ABS(F5)&lt;=2,"Satisfactorio",IF(ABS(F5)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2)=0),"",(D5-INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B5,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <f aca="false">IF(H5="","N/A",IF(ABS(H5)&lt;=2,"Satisfactorio",IF(ABS(H5)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E5^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2))),SQRT(E5^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2)=0),"",(D5-INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))/SQRT(E5^2+INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f aca="false">IF(J5="","N/A",IF(ABS(J5)&lt;=2,"Satisfactorio",IF(ABS(J5)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E5)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0)))^2))),SQRT((2*E5)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0)))^2)=0),"",(D5-INDEX(valor_asignado!$C:$C,MATCH(B5,valor_asignado!$B:$B,0)))/SQRT((2*E5)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B5,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="str">
+        <f aca="false">IF(L5="","N/A",IF(ABS(L5)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N5" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D5="",validacion_snapshot!$U$52=""),0,IFERROR(ABS(D5-validacion_snapshot!$U$52),1E+099)),IF(AND(E5="",validacion_snapshot!$V$52=""),0,IFERROR(ABS(E5-validacion_snapshot!$V$52),1E+099)),IF(AND(F5="",validacion_snapshot!$W$52=""),0,IFERROR(ABS(F5-validacion_snapshot!$W$52),1E+099)),IF(AND(H5="",validacion_snapshot!$Y$52=""),0,IFERROR(ABS(H5-validacion_snapshot!$Y$52),1E+099)),IF(AND(J5="",validacion_snapshot!$AA$52=""),0,IFERROR(ABS(J5-validacion_snapshot!$AA$52),1E+099)),IF(AND(L5="",validacion_snapshot!$AC$52=""),0,IFERROR(ABS(L5-validacion_snapshot!$AC$52),1E+099)))&lt;=0.00000001,G5=validacion_snapshot!$X$52,I5=validacion_snapshot!$Z$52,K5=validacion_snapshot!$AB$52,M5=validacion_snapshot!$AD$52),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C6,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C6,datos_participantes!$A:$A,0))</f>
+        <v>5.67577699037272E-006</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0))=0),"",(D6-INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="str">
+        <f aca="false">IF(F6="","N/A",IF(ABS(F6)&lt;=2,"Satisfactorio",IF(ABS(F6)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2)=0),"",(D6-INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B6,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <f aca="false">IF(H6="","N/A",IF(ABS(H6)&lt;=2,"Satisfactorio",IF(ABS(H6)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E6^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2))),SQRT(E6^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2)=0),"",(D6-INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))/SQRT(E6^2+INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="str">
+        <f aca="false">IF(J6="","N/A",IF(ABS(J6)&lt;=2,"Satisfactorio",IF(ABS(J6)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E6)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0)))^2))),SQRT((2*E6)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0)))^2)=0),"",(D6-INDEX(valor_asignado!$C:$C,MATCH(B6,valor_asignado!$B:$B,0)))/SQRT((2*E6)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B6,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="str">
+        <f aca="false">IF(L6="","N/A",IF(ABS(L6)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N6" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D6="",validacion_snapshot!$U$53=""),0,IFERROR(ABS(D6-validacion_snapshot!$U$53),1E+099)),IF(AND(E6="",validacion_snapshot!$V$53=""),0,IFERROR(ABS(E6-validacion_snapshot!$V$53),1E+099)),IF(AND(F6="",validacion_snapshot!$W$53=""),0,IFERROR(ABS(F6-validacion_snapshot!$W$53),1E+099)),IF(AND(H6="",validacion_snapshot!$Y$53=""),0,IFERROR(ABS(H6-validacion_snapshot!$Y$53),1E+099)),IF(AND(J6="",validacion_snapshot!$AA$53=""),0,IFERROR(ABS(J6-validacion_snapshot!$AA$53),1E+099)),IF(AND(L6="",validacion_snapshot!$AC$53=""),0,IFERROR(ABS(L6-validacion_snapshot!$AC$53),1E+099)))&lt;=0.00000001,G6=validacion_snapshot!$X$53,I6=validacion_snapshot!$Z$53,K6=validacion_snapshot!$AB$53,M6=validacion_snapshot!$AD$53),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C7,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C7,datos_participantes!$A:$A,0))</f>
+        <v>1.06666666666667E-006</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0))=0),"",(D7-INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="str">
+        <f aca="false">IF(F7="","N/A",IF(ABS(F7)&lt;=2,"Satisfactorio",IF(ABS(F7)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2)=0),"",(D7-INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B7,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="str">
+        <f aca="false">IF(H7="","N/A",IF(ABS(H7)&lt;=2,"Satisfactorio",IF(ABS(H7)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E7^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2))),SQRT(E7^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2)=0),"",(D7-INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))/SQRT(E7^2+INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f aca="false">IF(J7="","N/A",IF(ABS(J7)&lt;=2,"Satisfactorio",IF(ABS(J7)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E7)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0)))^2))),SQRT((2*E7)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0)))^2)=0),"",(D7-INDEX(valor_asignado!$C:$C,MATCH(B7,valor_asignado!$B:$B,0)))/SQRT((2*E7)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B7,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="str">
+        <f aca="false">IF(L7="","N/A",IF(ABS(L7)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N7" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D7="",validacion_snapshot!$U$54=""),0,IFERROR(ABS(D7-validacion_snapshot!$U$54),1E+099)),IF(AND(E7="",validacion_snapshot!$V$54=""),0,IFERROR(ABS(E7-validacion_snapshot!$V$54),1E+099)),IF(AND(F7="",validacion_snapshot!$W$54=""),0,IFERROR(ABS(F7-validacion_snapshot!$W$54),1E+099)),IF(AND(H7="",validacion_snapshot!$Y$54=""),0,IFERROR(ABS(H7-validacion_snapshot!$Y$54),1E+099)),IF(AND(J7="",validacion_snapshot!$AA$54=""),0,IFERROR(ABS(J7-validacion_snapshot!$AA$54),1E+099)),IF(AND(L7="",validacion_snapshot!$AC$54=""),0,IFERROR(ABS(L7-validacion_snapshot!$AC$54),1E+099)))&lt;=0.00000001,G7=validacion_snapshot!$X$54,I7=validacion_snapshot!$Z$54,K7=validacion_snapshot!$AB$54,M7=validacion_snapshot!$AD$54),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C8,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C8,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0))=0),"",(D8-INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="str">
+        <f aca="false">IF(F8="","N/A",IF(ABS(F8)&lt;=2,"Satisfactorio",IF(ABS(F8)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2)=0),"",(D8-INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B8,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="str">
+        <f aca="false">IF(H8="","N/A",IF(ABS(H8)&lt;=2,"Satisfactorio",IF(ABS(H8)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E8^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2))),SQRT(E8^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2)=0),"",(D8-INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))/SQRT(E8^2+INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="str">
+        <f aca="false">IF(J8="","N/A",IF(ABS(J8)&lt;=2,"Satisfactorio",IF(ABS(J8)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E8)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0)))^2))),SQRT((2*E8)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0)))^2)=0),"",(D8-INDEX(valor_asignado!$C:$C,MATCH(B8,valor_asignado!$B:$B,0)))/SQRT((2*E8)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B8,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="str">
+        <f aca="false">IF(L8="","N/A",IF(ABS(L8)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N8" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D8="",validacion_snapshot!$U$55=""),0,IFERROR(ABS(D8-validacion_snapshot!$U$55),1E+099)),IF(AND(E8="",validacion_snapshot!$V$55=""),0,IFERROR(ABS(E8-validacion_snapshot!$V$55),1E+099)),IF(AND(F8="",validacion_snapshot!$W$55=""),0,IFERROR(ABS(F8-validacion_snapshot!$W$55),1E+099)),IF(AND(H8="",validacion_snapshot!$Y$55=""),0,IFERROR(ABS(H8-validacion_snapshot!$Y$55),1E+099)),IF(AND(J8="",validacion_snapshot!$AA$55=""),0,IFERROR(ABS(J8-validacion_snapshot!$AA$55),1E+099)),IF(AND(L8="",validacion_snapshot!$AC$55=""),0,IFERROR(ABS(L8-validacion_snapshot!$AC$55),1E+099)))&lt;=0.00000001,G8=validacion_snapshot!$X$55,I8=validacion_snapshot!$Z$55,K8=validacion_snapshot!$AB$55,M8=validacion_snapshot!$AD$55),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C9,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C9,datos_participantes!$A:$A,0))</f>
+        <v>7.44781847254617E-006</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0))=0),"",(D9-INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="str">
+        <f aca="false">IF(F9="","N/A",IF(ABS(F9)&lt;=2,"Satisfactorio",IF(ABS(F9)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2)=0),"",(D9-INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B9,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="str">
+        <f aca="false">IF(H9="","N/A",IF(ABS(H9)&lt;=2,"Satisfactorio",IF(ABS(H9)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E9^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2))),SQRT(E9^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2)=0),"",(D9-INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))/SQRT(E9^2+INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f aca="false">IF(J9="","N/A",IF(ABS(J9)&lt;=2,"Satisfactorio",IF(ABS(J9)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E9)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0)))^2))),SQRT((2*E9)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0)))^2)=0),"",(D9-INDEX(valor_asignado!$C:$C,MATCH(B9,valor_asignado!$B:$B,0)))/SQRT((2*E9)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B9,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="str">
+        <f aca="false">IF(L9="","N/A",IF(ABS(L9)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N9" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D9="",validacion_snapshot!$U$56=""),0,IFERROR(ABS(D9-validacion_snapshot!$U$56),1E+099)),IF(AND(E9="",validacion_snapshot!$V$56=""),0,IFERROR(ABS(E9-validacion_snapshot!$V$56),1E+099)),IF(AND(F9="",validacion_snapshot!$W$56=""),0,IFERROR(ABS(F9-validacion_snapshot!$W$56),1E+099)),IF(AND(H9="",validacion_snapshot!$Y$56=""),0,IFERROR(ABS(H9-validacion_snapshot!$Y$56),1E+099)),IF(AND(J9="",validacion_snapshot!$AA$56=""),0,IFERROR(ABS(J9-validacion_snapshot!$AA$56),1E+099)),IF(AND(L9="",validacion_snapshot!$AC$56=""),0,IFERROR(ABS(L9-validacion_snapshot!$AC$56),1E+099)))&lt;=0.00000001,G9=validacion_snapshot!$X$56,I9=validacion_snapshot!$Z$56,K9=validacion_snapshot!$AB$56,M9=validacion_snapshot!$AD$56),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C10,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C10,datos_participantes!$A:$A,0))</f>
+        <v>2.84741598256696E-006</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0))=0),"",(D10-INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="str">
+        <f aca="false">IF(F10="","N/A",IF(ABS(F10)&lt;=2,"Satisfactorio",IF(ABS(F10)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2)=0),"",(D10-INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B10,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="str">
+        <f aca="false">IF(H10="","N/A",IF(ABS(H10)&lt;=2,"Satisfactorio",IF(ABS(H10)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E10^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2))),SQRT(E10^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2)=0),"",(D10-INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))/SQRT(E10^2+INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="str">
+        <f aca="false">IF(J10="","N/A",IF(ABS(J10)&lt;=2,"Satisfactorio",IF(ABS(J10)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E10)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0)))^2))),SQRT((2*E10)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0)))^2)=0),"",(D10-INDEX(valor_asignado!$C:$C,MATCH(B10,valor_asignado!$B:$B,0)))/SQRT((2*E10)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B10,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="str">
+        <f aca="false">IF(L10="","N/A",IF(ABS(L10)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N10" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D10="",validacion_snapshot!$U$57=""),0,IFERROR(ABS(D10-validacion_snapshot!$U$57),1E+099)),IF(AND(E10="",validacion_snapshot!$V$57=""),0,IFERROR(ABS(E10-validacion_snapshot!$V$57),1E+099)),IF(AND(F10="",validacion_snapshot!$W$57=""),0,IFERROR(ABS(F10-validacion_snapshot!$W$57),1E+099)),IF(AND(H10="",validacion_snapshot!$Y$57=""),0,IFERROR(ABS(H10-validacion_snapshot!$Y$57),1E+099)),IF(AND(J10="",validacion_snapshot!$AA$57=""),0,IFERROR(ABS(J10-validacion_snapshot!$AA$57),1E+099)),IF(AND(L10="",validacion_snapshot!$AC$57=""),0,IFERROR(ABS(L10-validacion_snapshot!$AC$57),1E+099)))&lt;=0.00000001,G10=validacion_snapshot!$X$57,I10=validacion_snapshot!$Z$57,K10=validacion_snapshot!$AB$57,M10=validacion_snapshot!$AD$57),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C11,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C11,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0))=0),"",(D11-INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="str">
+        <f aca="false">IF(F11="","N/A",IF(ABS(F11)&lt;=2,"Satisfactorio",IF(ABS(F11)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2)=0),"",(D11-INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B11,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="str">
+        <f aca="false">IF(H11="","N/A",IF(ABS(H11)&lt;=2,"Satisfactorio",IF(ABS(H11)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E11^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2))),SQRT(E11^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2)=0),"",(D11-INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))/SQRT(E11^2+INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="str">
+        <f aca="false">IF(J11="","N/A",IF(ABS(J11)&lt;=2,"Satisfactorio",IF(ABS(J11)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E11)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0)))^2))),SQRT((2*E11)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0)))^2)=0),"",(D11-INDEX(valor_asignado!$C:$C,MATCH(B11,valor_asignado!$B:$B,0)))/SQRT((2*E11)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B11,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="str">
+        <f aca="false">IF(L11="","N/A",IF(ABS(L11)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N11" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D11="",validacion_snapshot!$U$58=""),0,IFERROR(ABS(D11-validacion_snapshot!$U$58),1E+099)),IF(AND(E11="",validacion_snapshot!$V$58=""),0,IFERROR(ABS(E11-validacion_snapshot!$V$58),1E+099)),IF(AND(F11="",validacion_snapshot!$W$58=""),0,IFERROR(ABS(F11-validacion_snapshot!$W$58),1E+099)),IF(AND(H11="",validacion_snapshot!$Y$58=""),0,IFERROR(ABS(H11-validacion_snapshot!$Y$58),1E+099)),IF(AND(J11="",validacion_snapshot!$AA$58=""),0,IFERROR(ABS(J11-validacion_snapshot!$AA$58),1E+099)),IF(AND(L11="",validacion_snapshot!$AC$58=""),0,IFERROR(ABS(L11-validacion_snapshot!$AC$58),1E+099)))&lt;=0.00000001,G11=validacion_snapshot!$X$58,I11=validacion_snapshot!$Z$58,K11=validacion_snapshot!$AB$58,M11=validacion_snapshot!$AD$58),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C12,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C12,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0))=0),"",(D12-INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="str">
+        <f aca="false">IF(F12="","N/A",IF(ABS(F12)&lt;=2,"Satisfactorio",IF(ABS(F12)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2)=0),"",(D12-INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B12,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="str">
+        <f aca="false">IF(H12="","N/A",IF(ABS(H12)&lt;=2,"Satisfactorio",IF(ABS(H12)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E12^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2))),SQRT(E12^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2)=0),"",(D12-INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))/SQRT(E12^2+INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="str">
+        <f aca="false">IF(J12="","N/A",IF(ABS(J12)&lt;=2,"Satisfactorio",IF(ABS(J12)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E12)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0)))^2))),SQRT((2*E12)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0)))^2)=0),"",(D12-INDEX(valor_asignado!$C:$C,MATCH(B12,valor_asignado!$B:$B,0)))/SQRT((2*E12)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B12,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="str">
+        <f aca="false">IF(L12="","N/A",IF(ABS(L12)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N12" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D12="",validacion_snapshot!$U$59=""),0,IFERROR(ABS(D12-validacion_snapshot!$U$59),1E+099)),IF(AND(E12="",validacion_snapshot!$V$59=""),0,IFERROR(ABS(E12-validacion_snapshot!$V$59),1E+099)),IF(AND(F12="",validacion_snapshot!$W$59=""),0,IFERROR(ABS(F12-validacion_snapshot!$W$59),1E+099)),IF(AND(H12="",validacion_snapshot!$Y$59=""),0,IFERROR(ABS(H12-validacion_snapshot!$Y$59),1E+099)),IF(AND(J12="",validacion_snapshot!$AA$59=""),0,IFERROR(ABS(J12-validacion_snapshot!$AA$59),1E+099)),IF(AND(L12="",validacion_snapshot!$AC$59=""),0,IFERROR(ABS(L12-validacion_snapshot!$AC$59),1E+099)))&lt;=0.00000001,G12=validacion_snapshot!$X$59,I12=validacion_snapshot!$Z$59,K12=validacion_snapshot!$AB$59,M12=validacion_snapshot!$AD$59),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C13,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C13,datos_participantes!$A:$A,0))</f>
+        <v>1.16255943695127E-005</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0))=0),"",(D13-INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="str">
+        <f aca="false">IF(F13="","N/A",IF(ABS(F13)&lt;=2,"Satisfactorio",IF(ABS(F13)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2)=0),"",(D13-INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B13,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="str">
+        <f aca="false">IF(H13="","N/A",IF(ABS(H13)&lt;=2,"Satisfactorio",IF(ABS(H13)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E13^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2))),SQRT(E13^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2)=0),"",(D13-INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))/SQRT(E13^2+INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f aca="false">IF(J13="","N/A",IF(ABS(J13)&lt;=2,"Satisfactorio",IF(ABS(J13)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E13)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0)))^2))),SQRT((2*E13)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0)))^2)=0),"",(D13-INDEX(valor_asignado!$C:$C,MATCH(B13,valor_asignado!$B:$B,0)))/SQRT((2*E13)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B13,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="str">
+        <f aca="false">IF(L13="","N/A",IF(ABS(L13)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N13" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D13="",validacion_snapshot!$U$60=""),0,IFERROR(ABS(D13-validacion_snapshot!$U$60),1E+099)),IF(AND(E13="",validacion_snapshot!$V$60=""),0,IFERROR(ABS(E13-validacion_snapshot!$V$60),1E+099)),IF(AND(F13="",validacion_snapshot!$W$60=""),0,IFERROR(ABS(F13-validacion_snapshot!$W$60),1E+099)),IF(AND(H13="",validacion_snapshot!$Y$60=""),0,IFERROR(ABS(H13-validacion_snapshot!$Y$60),1E+099)),IF(AND(J13="",validacion_snapshot!$AA$60=""),0,IFERROR(ABS(J13-validacion_snapshot!$AA$60),1E+099)),IF(AND(L13="",validacion_snapshot!$AC$60=""),0,IFERROR(ABS(L13-validacion_snapshot!$AC$60),1E+099)))&lt;=0.00000001,G13=validacion_snapshot!$X$60,I13=validacion_snapshot!$Z$60,K13=validacion_snapshot!$AB$60,M13=validacion_snapshot!$AD$60),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C14,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C14,datos_participantes!$A:$A,0))</f>
+        <v>5.36666666666667E-006</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0))=0),"",(D14-INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G14" s="5" t="str">
+        <f aca="false">IF(F14="","N/A",IF(ABS(F14)&lt;=2,"Satisfactorio",IF(ABS(F14)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2)=0),"",(D14-INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B14,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I14" s="5" t="str">
+        <f aca="false">IF(H14="","N/A",IF(ABS(H14)&lt;=2,"Satisfactorio",IF(ABS(H14)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E14^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2))),SQRT(E14^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2)=0),"",(D14-INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))/SQRT(E14^2+INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f aca="false">IF(J14="","N/A",IF(ABS(J14)&lt;=2,"Satisfactorio",IF(ABS(J14)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E14)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0)))^2))),SQRT((2*E14)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0)))^2)=0),"",(D14-INDEX(valor_asignado!$C:$C,MATCH(B14,valor_asignado!$B:$B,0)))/SQRT((2*E14)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B14,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="str">
+        <f aca="false">IF(L14="","N/A",IF(ABS(L14)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N14" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D14="",validacion_snapshot!$U$61=""),0,IFERROR(ABS(D14-validacion_snapshot!$U$61),1E+099)),IF(AND(E14="",validacion_snapshot!$V$61=""),0,IFERROR(ABS(E14-validacion_snapshot!$V$61),1E+099)),IF(AND(F14="",validacion_snapshot!$W$61=""),0,IFERROR(ABS(F14-validacion_snapshot!$W$61),1E+099)),IF(AND(H14="",validacion_snapshot!$Y$61=""),0,IFERROR(ABS(H14-validacion_snapshot!$Y$61),1E+099)),IF(AND(J14="",validacion_snapshot!$AA$61=""),0,IFERROR(ABS(J14-validacion_snapshot!$AA$61),1E+099)),IF(AND(L14="",validacion_snapshot!$AC$61=""),0,IFERROR(ABS(L14-validacion_snapshot!$AC$61),1E+099)))&lt;=0.00000001,G14=validacion_snapshot!$X$61,I14=validacion_snapshot!$Z$61,K14=validacion_snapshot!$AB$61,M14=validacion_snapshot!$AD$61),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C15,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C15,datos_participantes!$A:$A,0))</f>
+        <v>1.8475208614068E-006</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0))=0),"",(D15-INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G15" s="5" t="str">
+        <f aca="false">IF(F15="","N/A",IF(ABS(F15)&lt;=2,"Satisfactorio",IF(ABS(F15)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H15" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2)=0),"",(D15-INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B15,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I15" s="5" t="str">
+        <f aca="false">IF(H15="","N/A",IF(ABS(H15)&lt;=2,"Satisfactorio",IF(ABS(H15)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E15^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2))),SQRT(E15^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2)=0),"",(D15-INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))/SQRT(E15^2+INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f aca="false">IF(J15="","N/A",IF(ABS(J15)&lt;=2,"Satisfactorio",IF(ABS(J15)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E15)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0)))^2))),SQRT((2*E15)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0)))^2)=0),"",(D15-INDEX(valor_asignado!$C:$C,MATCH(B15,valor_asignado!$B:$B,0)))/SQRT((2*E15)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B15,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="str">
+        <f aca="false">IF(L15="","N/A",IF(ABS(L15)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N15" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D15="",validacion_snapshot!$U$62=""),0,IFERROR(ABS(D15-validacion_snapshot!$U$62),1E+099)),IF(AND(E15="",validacion_snapshot!$V$62=""),0,IFERROR(ABS(E15-validacion_snapshot!$V$62),1E+099)),IF(AND(F15="",validacion_snapshot!$W$62=""),0,IFERROR(ABS(F15-validacion_snapshot!$W$62),1E+099)),IF(AND(H15="",validacion_snapshot!$Y$62=""),0,IFERROR(ABS(H15-validacion_snapshot!$Y$62),1E+099)),IF(AND(J15="",validacion_snapshot!$AA$62=""),0,IFERROR(ABS(J15-validacion_snapshot!$AA$62),1E+099)),IF(AND(L15="",validacion_snapshot!$AC$62=""),0,IFERROR(ABS(L15-validacion_snapshot!$AC$62),1E+099)))&lt;=0.00000001,G15=validacion_snapshot!$X$62,I15=validacion_snapshot!$Z$62,K15=validacion_snapshot!$AB$62,M15=validacion_snapshot!$AD$62),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C16,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C16,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0))=0),"",(D16-INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G16" s="5" t="str">
+        <f aca="false">IF(F16="","N/A",IF(ABS(F16)&lt;=2,"Satisfactorio",IF(ABS(F16)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2)=0),"",(D16-INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B16,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I16" s="5" t="str">
+        <f aca="false">IF(H16="","N/A",IF(ABS(H16)&lt;=2,"Satisfactorio",IF(ABS(H16)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E16^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2))),SQRT(E16^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2)=0),"",(D16-INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))/SQRT(E16^2+INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f aca="false">IF(J16="","N/A",IF(ABS(J16)&lt;=2,"Satisfactorio",IF(ABS(J16)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E16)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0)))^2))),SQRT((2*E16)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0)))^2)=0),"",(D16-INDEX(valor_asignado!$C:$C,MATCH(B16,valor_asignado!$B:$B,0)))/SQRT((2*E16)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B16,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f aca="false">IF(L16="","N/A",IF(ABS(L16)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N16" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D16="",validacion_snapshot!$U$63=""),0,IFERROR(ABS(D16-validacion_snapshot!$U$63),1E+099)),IF(AND(E16="",validacion_snapshot!$V$63=""),0,IFERROR(ABS(E16-validacion_snapshot!$V$63),1E+099)),IF(AND(F16="",validacion_snapshot!$W$63=""),0,IFERROR(ABS(F16-validacion_snapshot!$W$63),1E+099)),IF(AND(H16="",validacion_snapshot!$Y$63=""),0,IFERROR(ABS(H16-validacion_snapshot!$Y$63),1E+099)),IF(AND(J16="",validacion_snapshot!$AA$63=""),0,IFERROR(ABS(J16-validacion_snapshot!$AA$63),1E+099)),IF(AND(L16="",validacion_snapshot!$AC$63=""),0,IFERROR(ABS(L16-validacion_snapshot!$AC$63),1E+099)))&lt;=0.00000001,G16=validacion_snapshot!$X$63,I16=validacion_snapshot!$Z$63,K16=validacion_snapshot!$AB$63,M16=validacion_snapshot!$AD$63),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C17,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C17,datos_participantes!$A:$A,0))</f>
+        <v>6.69336321374473E-006</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0))=0),"",(D17-INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G17" s="5" t="str">
+        <f aca="false">IF(F17="","N/A",IF(ABS(F17)&lt;=2,"Satisfactorio",IF(ABS(F17)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H17" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2)=0),"",(D17-INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B17,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I17" s="5" t="str">
+        <f aca="false">IF(H17="","N/A",IF(ABS(H17)&lt;=2,"Satisfactorio",IF(ABS(H17)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E17^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2))),SQRT(E17^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2)=0),"",(D17-INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))/SQRT(E17^2+INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="str">
+        <f aca="false">IF(J17="","N/A",IF(ABS(J17)&lt;=2,"Satisfactorio",IF(ABS(J17)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E17)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0)))^2))),SQRT((2*E17)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0)))^2)=0),"",(D17-INDEX(valor_asignado!$C:$C,MATCH(B17,valor_asignado!$B:$B,0)))/SQRT((2*E17)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B17,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="str">
+        <f aca="false">IF(L17="","N/A",IF(ABS(L17)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N17" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D17="",validacion_snapshot!$U$64=""),0,IFERROR(ABS(D17-validacion_snapshot!$U$64),1E+099)),IF(AND(E17="",validacion_snapshot!$V$64=""),0,IFERROR(ABS(E17-validacion_snapshot!$V$64),1E+099)),IF(AND(F17="",validacion_snapshot!$W$64=""),0,IFERROR(ABS(F17-validacion_snapshot!$W$64),1E+099)),IF(AND(H17="",validacion_snapshot!$Y$64=""),0,IFERROR(ABS(H17-validacion_snapshot!$Y$64),1E+099)),IF(AND(J17="",validacion_snapshot!$AA$64=""),0,IFERROR(ABS(J17-validacion_snapshot!$AA$64),1E+099)),IF(AND(L17="",validacion_snapshot!$AC$64=""),0,IFERROR(ABS(L17-validacion_snapshot!$AC$64),1E+099)))&lt;=0.00000001,G17=validacion_snapshot!$X$64,I17=validacion_snapshot!$Z$64,K17=validacion_snapshot!$AB$64,M17=validacion_snapshot!$AD$64),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C18,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C18,datos_participantes!$A:$A,0))</f>
+        <v>5.67577699037272E-006</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0))=0),"",(D18-INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G18" s="5" t="str">
+        <f aca="false">IF(F18="","N/A",IF(ABS(F18)&lt;=2,"Satisfactorio",IF(ABS(F18)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2)=0),"",(D18-INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B18,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I18" s="5" t="str">
+        <f aca="false">IF(H18="","N/A",IF(ABS(H18)&lt;=2,"Satisfactorio",IF(ABS(H18)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E18^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2))),SQRT(E18^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2)=0),"",(D18-INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))/SQRT(E18^2+INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="str">
+        <f aca="false">IF(J18="","N/A",IF(ABS(J18)&lt;=2,"Satisfactorio",IF(ABS(J18)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E18)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0)))^2))),SQRT((2*E18)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0)))^2)=0),"",(D18-INDEX(valor_asignado!$C:$C,MATCH(B18,valor_asignado!$B:$B,0)))/SQRT((2*E18)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B18,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="str">
+        <f aca="false">IF(L18="","N/A",IF(ABS(L18)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N18" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D18="",validacion_snapshot!$U$65=""),0,IFERROR(ABS(D18-validacion_snapshot!$U$65),1E+099)),IF(AND(E18="",validacion_snapshot!$V$65=""),0,IFERROR(ABS(E18-validacion_snapshot!$V$65),1E+099)),IF(AND(F18="",validacion_snapshot!$W$65=""),0,IFERROR(ABS(F18-validacion_snapshot!$W$65),1E+099)),IF(AND(H18="",validacion_snapshot!$Y$65=""),0,IFERROR(ABS(H18-validacion_snapshot!$Y$65),1E+099)),IF(AND(J18="",validacion_snapshot!$AA$65=""),0,IFERROR(ABS(J18-validacion_snapshot!$AA$65),1E+099)),IF(AND(L18="",validacion_snapshot!$AC$65=""),0,IFERROR(ABS(L18-validacion_snapshot!$AC$65),1E+099)))&lt;=0.00000001,G18=validacion_snapshot!$X$65,I18=validacion_snapshot!$Z$65,K18=validacion_snapshot!$AB$65,M18=validacion_snapshot!$AD$65),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C19,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C19,datos_participantes!$A:$A,0))</f>
+        <v>1.06666666666667E-006</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0))=0),"",(D19-INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="5" t="str">
+        <f aca="false">IF(F19="","N/A",IF(ABS(F19)&lt;=2,"Satisfactorio",IF(ABS(F19)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H19" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2)=0),"",(D19-INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B19,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I19" s="5" t="str">
+        <f aca="false">IF(H19="","N/A",IF(ABS(H19)&lt;=2,"Satisfactorio",IF(ABS(H19)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E19^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2))),SQRT(E19^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2)=0),"",(D19-INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))/SQRT(E19^2+INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="str">
+        <f aca="false">IF(J19="","N/A",IF(ABS(J19)&lt;=2,"Satisfactorio",IF(ABS(J19)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E19)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0)))^2))),SQRT((2*E19)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0)))^2)=0),"",(D19-INDEX(valor_asignado!$C:$C,MATCH(B19,valor_asignado!$B:$B,0)))/SQRT((2*E19)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B19,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="str">
+        <f aca="false">IF(L19="","N/A",IF(ABS(L19)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N19" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D19="",validacion_snapshot!$U$66=""),0,IFERROR(ABS(D19-validacion_snapshot!$U$66),1E+099)),IF(AND(E19="",validacion_snapshot!$V$66=""),0,IFERROR(ABS(E19-validacion_snapshot!$V$66),1E+099)),IF(AND(F19="",validacion_snapshot!$W$66=""),0,IFERROR(ABS(F19-validacion_snapshot!$W$66),1E+099)),IF(AND(H19="",validacion_snapshot!$Y$66=""),0,IFERROR(ABS(H19-validacion_snapshot!$Y$66),1E+099)),IF(AND(J19="",validacion_snapshot!$AA$66=""),0,IFERROR(ABS(J19-validacion_snapshot!$AA$66),1E+099)),IF(AND(L19="",validacion_snapshot!$AC$66=""),0,IFERROR(ABS(L19-validacion_snapshot!$AC$66),1E+099)))&lt;=0.00000001,G19=validacion_snapshot!$X$66,I19=validacion_snapshot!$Z$66,K19=validacion_snapshot!$AB$66,M19=validacion_snapshot!$AD$66),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C20,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C20,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0))=0),"",(D20-INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="5" t="str">
+        <f aca="false">IF(F20="","N/A",IF(ABS(F20)&lt;=2,"Satisfactorio",IF(ABS(F20)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2)=0),"",(D20-INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B20,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I20" s="5" t="str">
+        <f aca="false">IF(H20="","N/A",IF(ABS(H20)&lt;=2,"Satisfactorio",IF(ABS(H20)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E20^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2))),SQRT(E20^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2)=0),"",(D20-INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))/SQRT(E20^2+INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f aca="false">IF(J20="","N/A",IF(ABS(J20)&lt;=2,"Satisfactorio",IF(ABS(J20)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E20)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0)))^2))),SQRT((2*E20)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0)))^2)=0),"",(D20-INDEX(valor_asignado!$C:$C,MATCH(B20,valor_asignado!$B:$B,0)))/SQRT((2*E20)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B20,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="str">
+        <f aca="false">IF(L20="","N/A",IF(ABS(L20)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N20" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D20="",validacion_snapshot!$U$67=""),0,IFERROR(ABS(D20-validacion_snapshot!$U$67),1E+099)),IF(AND(E20="",validacion_snapshot!$V$67=""),0,IFERROR(ABS(E20-validacion_snapshot!$V$67),1E+099)),IF(AND(F20="",validacion_snapshot!$W$67=""),0,IFERROR(ABS(F20-validacion_snapshot!$W$67),1E+099)),IF(AND(H20="",validacion_snapshot!$Y$67=""),0,IFERROR(ABS(H20-validacion_snapshot!$Y$67),1E+099)),IF(AND(J20="",validacion_snapshot!$AA$67=""),0,IFERROR(ABS(J20-validacion_snapshot!$AA$67),1E+099)),IF(AND(L20="",validacion_snapshot!$AC$67=""),0,IFERROR(ABS(L20-validacion_snapshot!$AC$67),1E+099)))&lt;=0.00000001,G20=validacion_snapshot!$X$67,I20=validacion_snapshot!$Z$67,K20=validacion_snapshot!$AB$67,M20=validacion_snapshot!$AD$67),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C21,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C21,datos_participantes!$A:$A,0))</f>
+        <v>7.44781847254617E-006</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0))=0),"",(D21-INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="5" t="str">
+        <f aca="false">IF(F21="","N/A",IF(ABS(F21)&lt;=2,"Satisfactorio",IF(ABS(F21)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H21" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2)=0),"",(D21-INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B21,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I21" s="5" t="str">
+        <f aca="false">IF(H21="","N/A",IF(ABS(H21)&lt;=2,"Satisfactorio",IF(ABS(H21)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E21^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2))),SQRT(E21^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2)=0),"",(D21-INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))/SQRT(E21^2+INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="str">
+        <f aca="false">IF(J21="","N/A",IF(ABS(J21)&lt;=2,"Satisfactorio",IF(ABS(J21)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E21)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0)))^2))),SQRT((2*E21)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0)))^2)=0),"",(D21-INDEX(valor_asignado!$C:$C,MATCH(B21,valor_asignado!$B:$B,0)))/SQRT((2*E21)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B21,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="str">
+        <f aca="false">IF(L21="","N/A",IF(ABS(L21)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N21" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D21="",validacion_snapshot!$U$68=""),0,IFERROR(ABS(D21-validacion_snapshot!$U$68),1E+099)),IF(AND(E21="",validacion_snapshot!$V$68=""),0,IFERROR(ABS(E21-validacion_snapshot!$V$68),1E+099)),IF(AND(F21="",validacion_snapshot!$W$68=""),0,IFERROR(ABS(F21-validacion_snapshot!$W$68),1E+099)),IF(AND(H21="",validacion_snapshot!$Y$68=""),0,IFERROR(ABS(H21-validacion_snapshot!$Y$68),1E+099)),IF(AND(J21="",validacion_snapshot!$AA$68=""),0,IFERROR(ABS(J21-validacion_snapshot!$AA$68),1E+099)),IF(AND(L21="",validacion_snapshot!$AC$68=""),0,IFERROR(ABS(L21-validacion_snapshot!$AC$68),1E+099)))&lt;=0.00000001,G21=validacion_snapshot!$X$68,I21=validacion_snapshot!$Z$68,K21=validacion_snapshot!$AB$68,M21=validacion_snapshot!$AD$68),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C22,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C22,datos_participantes!$A:$A,0))</f>
+        <v>2.84741598256696E-006</v>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0))=0),"",(D22-INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="5" t="str">
+        <f aca="false">IF(F22="","N/A",IF(ABS(F22)&lt;=2,"Satisfactorio",IF(ABS(F22)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2)=0),"",(D22-INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B22,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I22" s="5" t="str">
+        <f aca="false">IF(H22="","N/A",IF(ABS(H22)&lt;=2,"Satisfactorio",IF(ABS(H22)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E22^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2))),SQRT(E22^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2)=0),"",(D22-INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))/SQRT(E22^2+INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="str">
+        <f aca="false">IF(J22="","N/A",IF(ABS(J22)&lt;=2,"Satisfactorio",IF(ABS(J22)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E22)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0)))^2))),SQRT((2*E22)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0)))^2)=0),"",(D22-INDEX(valor_asignado!$C:$C,MATCH(B22,valor_asignado!$B:$B,0)))/SQRT((2*E22)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B22,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="str">
+        <f aca="false">IF(L22="","N/A",IF(ABS(L22)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N22" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D22="",validacion_snapshot!$U$69=""),0,IFERROR(ABS(D22-validacion_snapshot!$U$69),1E+099)),IF(AND(E22="",validacion_snapshot!$V$69=""),0,IFERROR(ABS(E22-validacion_snapshot!$V$69),1E+099)),IF(AND(F22="",validacion_snapshot!$W$69=""),0,IFERROR(ABS(F22-validacion_snapshot!$W$69),1E+099)),IF(AND(H22="",validacion_snapshot!$Y$69=""),0,IFERROR(ABS(H22-validacion_snapshot!$Y$69),1E+099)),IF(AND(J22="",validacion_snapshot!$AA$69=""),0,IFERROR(ABS(J22-validacion_snapshot!$AA$69),1E+099)),IF(AND(L22="",validacion_snapshot!$AC$69=""),0,IFERROR(ABS(L22-validacion_snapshot!$AC$69),1E+099)))&lt;=0.00000001,G22=validacion_snapshot!$X$69,I22=validacion_snapshot!$Z$69,K22=validacion_snapshot!$AB$69,M22=validacion_snapshot!$AD$69),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C23,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C23,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F23" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0))=0),"",(D23-INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="5" t="str">
+        <f aca="false">IF(F23="","N/A",IF(ABS(F23)&lt;=2,"Satisfactorio",IF(ABS(F23)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H23" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2)=0),"",(D23-INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B23,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I23" s="5" t="str">
+        <f aca="false">IF(H23="","N/A",IF(ABS(H23)&lt;=2,"Satisfactorio",IF(ABS(H23)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E23^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2))),SQRT(E23^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2)=0),"",(D23-INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))/SQRT(E23^2+INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f aca="false">IF(J23="","N/A",IF(ABS(J23)&lt;=2,"Satisfactorio",IF(ABS(J23)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E23)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0)))^2))),SQRT((2*E23)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0)))^2)=0),"",(D23-INDEX(valor_asignado!$C:$C,MATCH(B23,valor_asignado!$B:$B,0)))/SQRT((2*E23)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B23,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f aca="false">IF(L23="","N/A",IF(ABS(L23)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D23="",validacion_snapshot!$U$70=""),0,IFERROR(ABS(D23-validacion_snapshot!$U$70),1E+099)),IF(AND(E23="",validacion_snapshot!$V$70=""),0,IFERROR(ABS(E23-validacion_snapshot!$V$70),1E+099)),IF(AND(F23="",validacion_snapshot!$W$70=""),0,IFERROR(ABS(F23-validacion_snapshot!$W$70),1E+099)),IF(AND(H23="",validacion_snapshot!$Y$70=""),0,IFERROR(ABS(H23-validacion_snapshot!$Y$70),1E+099)),IF(AND(J23="",validacion_snapshot!$AA$70=""),0,IFERROR(ABS(J23-validacion_snapshot!$AA$70),1E+099)),IF(AND(L23="",validacion_snapshot!$AC$70=""),0,IFERROR(ABS(L23-validacion_snapshot!$AC$70),1E+099)))&lt;=0.00000001,G23=validacion_snapshot!$X$70,I23=validacion_snapshot!$Z$70,K23=validacion_snapshot!$AB$70,M23=validacion_snapshot!$AD$70),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C24,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C24,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0))=0),"",(D24-INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="5" t="str">
+        <f aca="false">IF(F24="","N/A",IF(ABS(F24)&lt;=2,"Satisfactorio",IF(ABS(F24)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2)=0),"",(D24-INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B24,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I24" s="5" t="str">
+        <f aca="false">IF(H24="","N/A",IF(ABS(H24)&lt;=2,"Satisfactorio",IF(ABS(H24)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E24^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2))),SQRT(E24^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2)=0),"",(D24-INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))/SQRT(E24^2+INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f aca="false">IF(J24="","N/A",IF(ABS(J24)&lt;=2,"Satisfactorio",IF(ABS(J24)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E24)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0)))^2))),SQRT((2*E24)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0)))^2)=0),"",(D24-INDEX(valor_asignado!$C:$C,MATCH(B24,valor_asignado!$B:$B,0)))/SQRT((2*E24)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B24,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="str">
+        <f aca="false">IF(L24="","N/A",IF(ABS(L24)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N24" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D24="",validacion_snapshot!$U$71=""),0,IFERROR(ABS(D24-validacion_snapshot!$U$71),1E+099)),IF(AND(E24="",validacion_snapshot!$V$71=""),0,IFERROR(ABS(E24-validacion_snapshot!$V$71),1E+099)),IF(AND(F24="",validacion_snapshot!$W$71=""),0,IFERROR(ABS(F24-validacion_snapshot!$W$71),1E+099)),IF(AND(H24="",validacion_snapshot!$Y$71=""),0,IFERROR(ABS(H24-validacion_snapshot!$Y$71),1E+099)),IF(AND(J24="",validacion_snapshot!$AA$71=""),0,IFERROR(ABS(J24-validacion_snapshot!$AA$71),1E+099)),IF(AND(L24="",validacion_snapshot!$AC$71=""),0,IFERROR(ABS(L24-validacion_snapshot!$AC$71),1E+099)))&lt;=0.00000001,G24=validacion_snapshot!$X$71,I24=validacion_snapshot!$Z$71,K24=validacion_snapshot!$AB$71,M24=validacion_snapshot!$AD$71),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C25,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C25,datos_participantes!$A:$A,0))</f>
+        <v>1.16255943695127E-005</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0))=0),"",(D25-INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="5" t="str">
+        <f aca="false">IF(F25="","N/A",IF(ABS(F25)&lt;=2,"Satisfactorio",IF(ABS(F25)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H25" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2)=0),"",(D25-INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B25,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I25" s="5" t="str">
+        <f aca="false">IF(H25="","N/A",IF(ABS(H25)&lt;=2,"Satisfactorio",IF(ABS(H25)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E25^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2))),SQRT(E25^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2)=0),"",(D25-INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))/SQRT(E25^2+INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="str">
+        <f aca="false">IF(J25="","N/A",IF(ABS(J25)&lt;=2,"Satisfactorio",IF(ABS(J25)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E25)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0)))^2))),SQRT((2*E25)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0)))^2)=0),"",(D25-INDEX(valor_asignado!$C:$C,MATCH(B25,valor_asignado!$B:$B,0)))/SQRT((2*E25)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B25,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="str">
+        <f aca="false">IF(L25="","N/A",IF(ABS(L25)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N25" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D25="",validacion_snapshot!$U$72=""),0,IFERROR(ABS(D25-validacion_snapshot!$U$72),1E+099)),IF(AND(E25="",validacion_snapshot!$V$72=""),0,IFERROR(ABS(E25-validacion_snapshot!$V$72),1E+099)),IF(AND(F25="",validacion_snapshot!$W$72=""),0,IFERROR(ABS(F25-validacion_snapshot!$W$72),1E+099)),IF(AND(H25="",validacion_snapshot!$Y$72=""),0,IFERROR(ABS(H25-validacion_snapshot!$Y$72),1E+099)),IF(AND(J25="",validacion_snapshot!$AA$72=""),0,IFERROR(ABS(J25-validacion_snapshot!$AA$72),1E+099)),IF(AND(L25="",validacion_snapshot!$AC$72=""),0,IFERROR(ABS(L25-validacion_snapshot!$AC$72),1E+099)))&lt;=0.00000001,G25=validacion_snapshot!$X$72,I25=validacion_snapshot!$Z$72,K25=validacion_snapshot!$AB$72,M25=validacion_snapshot!$AD$72),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C26,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C26,datos_participantes!$A:$A,0))</f>
+        <v>5.36666666666667E-006</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0))=0),"",(D26-INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="5" t="str">
+        <f aca="false">IF(F26="","N/A",IF(ABS(F26)&lt;=2,"Satisfactorio",IF(ABS(F26)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2)=0),"",(D26-INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B26,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I26" s="5" t="str">
+        <f aca="false">IF(H26="","N/A",IF(ABS(H26)&lt;=2,"Satisfactorio",IF(ABS(H26)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E26^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2))),SQRT(E26^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2)=0),"",(D26-INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))/SQRT(E26^2+INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f aca="false">IF(J26="","N/A",IF(ABS(J26)&lt;=2,"Satisfactorio",IF(ABS(J26)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E26)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0)))^2))),SQRT((2*E26)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0)))^2)=0),"",(D26-INDEX(valor_asignado!$C:$C,MATCH(B26,valor_asignado!$B:$B,0)))/SQRT((2*E26)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B26,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="str">
+        <f aca="false">IF(L26="","N/A",IF(ABS(L26)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N26" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D26="",validacion_snapshot!$U$73=""),0,IFERROR(ABS(D26-validacion_snapshot!$U$73),1E+099)),IF(AND(E26="",validacion_snapshot!$V$73=""),0,IFERROR(ABS(E26-validacion_snapshot!$V$73),1E+099)),IF(AND(F26="",validacion_snapshot!$W$73=""),0,IFERROR(ABS(F26-validacion_snapshot!$W$73),1E+099)),IF(AND(H26="",validacion_snapshot!$Y$73=""),0,IFERROR(ABS(H26-validacion_snapshot!$Y$73),1E+099)),IF(AND(J26="",validacion_snapshot!$AA$73=""),0,IFERROR(ABS(J26-validacion_snapshot!$AA$73),1E+099)),IF(AND(L26="",validacion_snapshot!$AC$73=""),0,IFERROR(ABS(L26-validacion_snapshot!$AC$73),1E+099)))&lt;=0.00000001,G26=validacion_snapshot!$X$73,I26=validacion_snapshot!$Z$73,K26=validacion_snapshot!$AB$73,M26=validacion_snapshot!$AD$73),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C27,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C27,datos_participantes!$A:$A,0))</f>
+        <v>1.8475208614068E-006</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0))=0),"",(D27-INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="5" t="str">
+        <f aca="false">IF(F27="","N/A",IF(ABS(F27)&lt;=2,"Satisfactorio",IF(ABS(F27)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2)=0),"",(D27-INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B27,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I27" s="5" t="str">
+        <f aca="false">IF(H27="","N/A",IF(ABS(H27)&lt;=2,"Satisfactorio",IF(ABS(H27)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E27^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2))),SQRT(E27^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2)=0),"",(D27-INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))/SQRT(E27^2+INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f aca="false">IF(J27="","N/A",IF(ABS(J27)&lt;=2,"Satisfactorio",IF(ABS(J27)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E27)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0)))^2))),SQRT((2*E27)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0)))^2)=0),"",(D27-INDEX(valor_asignado!$C:$C,MATCH(B27,valor_asignado!$B:$B,0)))/SQRT((2*E27)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B27,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="5" t="str">
+        <f aca="false">IF(L27="","N/A",IF(ABS(L27)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N27" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D27="",validacion_snapshot!$U$74=""),0,IFERROR(ABS(D27-validacion_snapshot!$U$74),1E+099)),IF(AND(E27="",validacion_snapshot!$V$74=""),0,IFERROR(ABS(E27-validacion_snapshot!$V$74),1E+099)),IF(AND(F27="",validacion_snapshot!$W$74=""),0,IFERROR(ABS(F27-validacion_snapshot!$W$74),1E+099)),IF(AND(H27="",validacion_snapshot!$Y$74=""),0,IFERROR(ABS(H27-validacion_snapshot!$Y$74),1E+099)),IF(AND(J27="",validacion_snapshot!$AA$74=""),0,IFERROR(ABS(J27-validacion_snapshot!$AA$74),1E+099)),IF(AND(L27="",validacion_snapshot!$AC$74=""),0,IFERROR(ABS(L27-validacion_snapshot!$AC$74),1E+099)))&lt;=0.00000001,G27=validacion_snapshot!$X$74,I27=validacion_snapshot!$Z$74,K27=validacion_snapshot!$AB$74,M27=validacion_snapshot!$AD$74),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C28,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C28,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0))=0),"",(D28-INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="5" t="str">
+        <f aca="false">IF(F28="","N/A",IF(ABS(F28)&lt;=2,"Satisfactorio",IF(ABS(F28)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2)=0),"",(D28-INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B28,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I28" s="5" t="str">
+        <f aca="false">IF(H28="","N/A",IF(ABS(H28)&lt;=2,"Satisfactorio",IF(ABS(H28)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E28^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2))),SQRT(E28^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2)=0),"",(D28-INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))/SQRT(E28^2+INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="str">
+        <f aca="false">IF(J28="","N/A",IF(ABS(J28)&lt;=2,"Satisfactorio",IF(ABS(J28)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E28)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0)))^2))),SQRT((2*E28)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0)))^2)=0),"",(D28-INDEX(valor_asignado!$C:$C,MATCH(B28,valor_asignado!$B:$B,0)))/SQRT((2*E28)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B28,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="5" t="str">
+        <f aca="false">IF(L28="","N/A",IF(ABS(L28)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N28" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D28="",validacion_snapshot!$U$75=""),0,IFERROR(ABS(D28-validacion_snapshot!$U$75),1E+099)),IF(AND(E28="",validacion_snapshot!$V$75=""),0,IFERROR(ABS(E28-validacion_snapshot!$V$75),1E+099)),IF(AND(F28="",validacion_snapshot!$W$75=""),0,IFERROR(ABS(F28-validacion_snapshot!$W$75),1E+099)),IF(AND(H28="",validacion_snapshot!$Y$75=""),0,IFERROR(ABS(H28-validacion_snapshot!$Y$75),1E+099)),IF(AND(J28="",validacion_snapshot!$AA$75=""),0,IFERROR(ABS(J28-validacion_snapshot!$AA$75),1E+099)),IF(AND(L28="",validacion_snapshot!$AC$75=""),0,IFERROR(ABS(L28-validacion_snapshot!$AC$75),1E+099)))&lt;=0.00000001,G28=validacion_snapshot!$X$75,I28=validacion_snapshot!$Z$75,K28=validacion_snapshot!$AB$75,M28=validacion_snapshot!$AD$75),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C29,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C29,datos_participantes!$A:$A,0))</f>
+        <v>6.69336321374473E-006</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0))=0),"",(D29-INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="5" t="str">
+        <f aca="false">IF(F29="","N/A",IF(ABS(F29)&lt;=2,"Satisfactorio",IF(ABS(F29)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2)=0),"",(D29-INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B29,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I29" s="5" t="str">
+        <f aca="false">IF(H29="","N/A",IF(ABS(H29)&lt;=2,"Satisfactorio",IF(ABS(H29)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E29^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2))),SQRT(E29^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2)=0),"",(D29-INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))/SQRT(E29^2+INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="str">
+        <f aca="false">IF(J29="","N/A",IF(ABS(J29)&lt;=2,"Satisfactorio",IF(ABS(J29)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E29)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0)))^2))),SQRT((2*E29)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0)))^2)=0),"",(D29-INDEX(valor_asignado!$C:$C,MATCH(B29,valor_asignado!$B:$B,0)))/SQRT((2*E29)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B29,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="5" t="str">
+        <f aca="false">IF(L29="","N/A",IF(ABS(L29)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N29" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D29="",validacion_snapshot!$U$76=""),0,IFERROR(ABS(D29-validacion_snapshot!$U$76),1E+099)),IF(AND(E29="",validacion_snapshot!$V$76=""),0,IFERROR(ABS(E29-validacion_snapshot!$V$76),1E+099)),IF(AND(F29="",validacion_snapshot!$W$76=""),0,IFERROR(ABS(F29-validacion_snapshot!$W$76),1E+099)),IF(AND(H29="",validacion_snapshot!$Y$76=""),0,IFERROR(ABS(H29-validacion_snapshot!$Y$76),1E+099)),IF(AND(J29="",validacion_snapshot!$AA$76=""),0,IFERROR(ABS(J29-validacion_snapshot!$AA$76),1E+099)),IF(AND(L29="",validacion_snapshot!$AC$76=""),0,IFERROR(ABS(L29-validacion_snapshot!$AC$76),1E+099)))&lt;=0.00000001,G29=validacion_snapshot!$X$76,I29=validacion_snapshot!$Z$76,K29=validacion_snapshot!$AB$76,M29=validacion_snapshot!$AD$76),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C30,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C30,datos_participantes!$A:$A,0))</f>
+        <v>5.67577699037272E-006</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0))=0),"",(D30-INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G30" s="5" t="str">
+        <f aca="false">IF(F30="","N/A",IF(ABS(F30)&lt;=2,"Satisfactorio",IF(ABS(F30)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2)=0),"",(D30-INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B30,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I30" s="5" t="str">
+        <f aca="false">IF(H30="","N/A",IF(ABS(H30)&lt;=2,"Satisfactorio",IF(ABS(H30)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E30^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2))),SQRT(E30^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2)=0),"",(D30-INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))/SQRT(E30^2+INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="str">
+        <f aca="false">IF(J30="","N/A",IF(ABS(J30)&lt;=2,"Satisfactorio",IF(ABS(J30)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E30)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0)))^2))),SQRT((2*E30)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0)))^2)=0),"",(D30-INDEX(valor_asignado!$C:$C,MATCH(B30,valor_asignado!$B:$B,0)))/SQRT((2*E30)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B30,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="str">
+        <f aca="false">IF(L30="","N/A",IF(ABS(L30)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N30" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D30="",validacion_snapshot!$U$77=""),0,IFERROR(ABS(D30-validacion_snapshot!$U$77),1E+099)),IF(AND(E30="",validacion_snapshot!$V$77=""),0,IFERROR(ABS(E30-validacion_snapshot!$V$77),1E+099)),IF(AND(F30="",validacion_snapshot!$W$77=""),0,IFERROR(ABS(F30-validacion_snapshot!$W$77),1E+099)),IF(AND(H30="",validacion_snapshot!$Y$77=""),0,IFERROR(ABS(H30-validacion_snapshot!$Y$77),1E+099)),IF(AND(J30="",validacion_snapshot!$AA$77=""),0,IFERROR(ABS(J30-validacion_snapshot!$AA$77),1E+099)),IF(AND(L30="",validacion_snapshot!$AC$77=""),0,IFERROR(ABS(L30-validacion_snapshot!$AC$77),1E+099)))&lt;=0.00000001,G30=validacion_snapshot!$X$77,I30=validacion_snapshot!$Z$77,K30=validacion_snapshot!$AB$77,M30=validacion_snapshot!$AD$77),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C31,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C31,datos_participantes!$A:$A,0))</f>
+        <v>1.06666666666667E-006</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0))=0),"",(D31-INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f aca="false">IF(F31="","N/A",IF(ABS(F31)&lt;=2,"Satisfactorio",IF(ABS(F31)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H31" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2)=0),"",(D31-INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B31,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I31" s="5" t="str">
+        <f aca="false">IF(H31="","N/A",IF(ABS(H31)&lt;=2,"Satisfactorio",IF(ABS(H31)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E31^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2))),SQRT(E31^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2)=0),"",(D31-INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))/SQRT(E31^2+INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="str">
+        <f aca="false">IF(J31="","N/A",IF(ABS(J31)&lt;=2,"Satisfactorio",IF(ABS(J31)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E31)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0)))^2))),SQRT((2*E31)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0)))^2)=0),"",(D31-INDEX(valor_asignado!$C:$C,MATCH(B31,valor_asignado!$B:$B,0)))/SQRT((2*E31)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B31,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="str">
+        <f aca="false">IF(L31="","N/A",IF(ABS(L31)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N31" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D31="",validacion_snapshot!$U$78=""),0,IFERROR(ABS(D31-validacion_snapshot!$U$78),1E+099)),IF(AND(E31="",validacion_snapshot!$V$78=""),0,IFERROR(ABS(E31-validacion_snapshot!$V$78),1E+099)),IF(AND(F31="",validacion_snapshot!$W$78=""),0,IFERROR(ABS(F31-validacion_snapshot!$W$78),1E+099)),IF(AND(H31="",validacion_snapshot!$Y$78=""),0,IFERROR(ABS(H31-validacion_snapshot!$Y$78),1E+099)),IF(AND(J31="",validacion_snapshot!$AA$78=""),0,IFERROR(ABS(J31-validacion_snapshot!$AA$78),1E+099)),IF(AND(L31="",validacion_snapshot!$AC$78=""),0,IFERROR(ABS(L31-validacion_snapshot!$AC$78),1E+099)))&lt;=0.00000001,G31=validacion_snapshot!$X$78,I31=validacion_snapshot!$Z$78,K31=validacion_snapshot!$AB$78,M31=validacion_snapshot!$AD$78),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C32,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C32,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0))=0),"",(D32-INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G32" s="5" t="str">
+        <f aca="false">IF(F32="","N/A",IF(ABS(F32)&lt;=2,"Satisfactorio",IF(ABS(F32)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2)=0),"",(D32-INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B32,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I32" s="5" t="str">
+        <f aca="false">IF(H32="","N/A",IF(ABS(H32)&lt;=2,"Satisfactorio",IF(ABS(H32)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E32^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2))),SQRT(E32^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2)=0),"",(D32-INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))/SQRT(E32^2+INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="str">
+        <f aca="false">IF(J32="","N/A",IF(ABS(J32)&lt;=2,"Satisfactorio",IF(ABS(J32)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E32)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0)))^2))),SQRT((2*E32)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0)))^2)=0),"",(D32-INDEX(valor_asignado!$C:$C,MATCH(B32,valor_asignado!$B:$B,0)))/SQRT((2*E32)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B32,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="str">
+        <f aca="false">IF(L32="","N/A",IF(ABS(L32)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N32" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D32="",validacion_snapshot!$U$79=""),0,IFERROR(ABS(D32-validacion_snapshot!$U$79),1E+099)),IF(AND(E32="",validacion_snapshot!$V$79=""),0,IFERROR(ABS(E32-validacion_snapshot!$V$79),1E+099)),IF(AND(F32="",validacion_snapshot!$W$79=""),0,IFERROR(ABS(F32-validacion_snapshot!$W$79),1E+099)),IF(AND(H32="",validacion_snapshot!$Y$79=""),0,IFERROR(ABS(H32-validacion_snapshot!$Y$79),1E+099)),IF(AND(J32="",validacion_snapshot!$AA$79=""),0,IFERROR(ABS(J32-validacion_snapshot!$AA$79),1E+099)),IF(AND(L32="",validacion_snapshot!$AC$79=""),0,IFERROR(ABS(L32-validacion_snapshot!$AC$79),1E+099)))&lt;=0.00000001,G32=validacion_snapshot!$X$79,I32=validacion_snapshot!$Z$79,K32=validacion_snapshot!$AB$79,M32=validacion_snapshot!$AD$79),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C33,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C33,datos_participantes!$A:$A,0))</f>
+        <v>7.44781847254617E-006</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0))=0),"",(D33-INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G33" s="5" t="str">
+        <f aca="false">IF(F33="","N/A",IF(ABS(F33)&lt;=2,"Satisfactorio",IF(ABS(F33)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H33" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2)=0),"",(D33-INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B33,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I33" s="5" t="str">
+        <f aca="false">IF(H33="","N/A",IF(ABS(H33)&lt;=2,"Satisfactorio",IF(ABS(H33)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E33^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2))),SQRT(E33^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2)=0),"",(D33-INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))/SQRT(E33^2+INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="str">
+        <f aca="false">IF(J33="","N/A",IF(ABS(J33)&lt;=2,"Satisfactorio",IF(ABS(J33)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E33)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0)))^2))),SQRT((2*E33)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0)))^2)=0),"",(D33-INDEX(valor_asignado!$C:$C,MATCH(B33,valor_asignado!$B:$B,0)))/SQRT((2*E33)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B33,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="5" t="str">
+        <f aca="false">IF(L33="","N/A",IF(ABS(L33)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N33" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D33="",validacion_snapshot!$U$80=""),0,IFERROR(ABS(D33-validacion_snapshot!$U$80),1E+099)),IF(AND(E33="",validacion_snapshot!$V$80=""),0,IFERROR(ABS(E33-validacion_snapshot!$V$80),1E+099)),IF(AND(F33="",validacion_snapshot!$W$80=""),0,IFERROR(ABS(F33-validacion_snapshot!$W$80),1E+099)),IF(AND(H33="",validacion_snapshot!$Y$80=""),0,IFERROR(ABS(H33-validacion_snapshot!$Y$80),1E+099)),IF(AND(J33="",validacion_snapshot!$AA$80=""),0,IFERROR(ABS(J33-validacion_snapshot!$AA$80),1E+099)),IF(AND(L33="",validacion_snapshot!$AC$80=""),0,IFERROR(ABS(L33-validacion_snapshot!$AC$80),1E+099)))&lt;=0.00000001,G33=validacion_snapshot!$X$80,I33=validacion_snapshot!$Z$80,K33=validacion_snapshot!$AB$80,M33=validacion_snapshot!$AD$80),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C34,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C34,datos_participantes!$A:$A,0))</f>
+        <v>2.84741598256696E-006</v>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0))=0),"",(D34-INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f aca="false">IF(F34="","N/A",IF(ABS(F34)&lt;=2,"Satisfactorio",IF(ABS(F34)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2)=0),"",(D34-INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B34,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I34" s="5" t="str">
+        <f aca="false">IF(H34="","N/A",IF(ABS(H34)&lt;=2,"Satisfactorio",IF(ABS(H34)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E34^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2))),SQRT(E34^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2)=0),"",(D34-INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))/SQRT(E34^2+INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f aca="false">IF(J34="","N/A",IF(ABS(J34)&lt;=2,"Satisfactorio",IF(ABS(J34)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E34)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0)))^2))),SQRT((2*E34)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0)))^2)=0),"",(D34-INDEX(valor_asignado!$C:$C,MATCH(B34,valor_asignado!$B:$B,0)))/SQRT((2*E34)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B34,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="str">
+        <f aca="false">IF(L34="","N/A",IF(ABS(L34)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N34" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D34="",validacion_snapshot!$U$81=""),0,IFERROR(ABS(D34-validacion_snapshot!$U$81),1E+099)),IF(AND(E34="",validacion_snapshot!$V$81=""),0,IFERROR(ABS(E34-validacion_snapshot!$V$81),1E+099)),IF(AND(F34="",validacion_snapshot!$W$81=""),0,IFERROR(ABS(F34-validacion_snapshot!$W$81),1E+099)),IF(AND(H34="",validacion_snapshot!$Y$81=""),0,IFERROR(ABS(H34-validacion_snapshot!$Y$81),1E+099)),IF(AND(J34="",validacion_snapshot!$AA$81=""),0,IFERROR(ABS(J34-validacion_snapshot!$AA$81),1E+099)),IF(AND(L34="",validacion_snapshot!$AC$81=""),0,IFERROR(ABS(L34-validacion_snapshot!$AC$81),1E+099)))&lt;=0.00000001,G34=validacion_snapshot!$X$81,I34=validacion_snapshot!$Z$81,K34=validacion_snapshot!$AB$81,M34=validacion_snapshot!$AD$81),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C35,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C35,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F35" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0))=0),"",(D35-INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G35" s="5" t="str">
+        <f aca="false">IF(F35="","N/A",IF(ABS(F35)&lt;=2,"Satisfactorio",IF(ABS(F35)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H35" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2)=0),"",(D35-INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B35,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I35" s="5" t="str">
+        <f aca="false">IF(H35="","N/A",IF(ABS(H35)&lt;=2,"Satisfactorio",IF(ABS(H35)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E35^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2))),SQRT(E35^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2)=0),"",(D35-INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))/SQRT(E35^2+INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="str">
+        <f aca="false">IF(J35="","N/A",IF(ABS(J35)&lt;=2,"Satisfactorio",IF(ABS(J35)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E35)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0)))^2))),SQRT((2*E35)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0)))^2)=0),"",(D35-INDEX(valor_asignado!$C:$C,MATCH(B35,valor_asignado!$B:$B,0)))/SQRT((2*E35)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B35,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="str">
+        <f aca="false">IF(L35="","N/A",IF(ABS(L35)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N35" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D35="",validacion_snapshot!$U$82=""),0,IFERROR(ABS(D35-validacion_snapshot!$U$82),1E+099)),IF(AND(E35="",validacion_snapshot!$V$82=""),0,IFERROR(ABS(E35-validacion_snapshot!$V$82),1E+099)),IF(AND(F35="",validacion_snapshot!$W$82=""),0,IFERROR(ABS(F35-validacion_snapshot!$W$82),1E+099)),IF(AND(H35="",validacion_snapshot!$Y$82=""),0,IFERROR(ABS(H35-validacion_snapshot!$Y$82),1E+099)),IF(AND(J35="",validacion_snapshot!$AA$82=""),0,IFERROR(ABS(J35-validacion_snapshot!$AA$82),1E+099)),IF(AND(L35="",validacion_snapshot!$AC$82=""),0,IFERROR(ABS(L35-validacion_snapshot!$AC$82),1E+099)))&lt;=0.00000001,G35=validacion_snapshot!$X$82,I35=validacion_snapshot!$Z$82,K35=validacion_snapshot!$AB$82,M35=validacion_snapshot!$AD$82),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C36,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C36,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0))=0),"",(D36-INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G36" s="5" t="str">
+        <f aca="false">IF(F36="","N/A",IF(ABS(F36)&lt;=2,"Satisfactorio",IF(ABS(F36)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2)=0),"",(D36-INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B36,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I36" s="5" t="str">
+        <f aca="false">IF(H36="","N/A",IF(ABS(H36)&lt;=2,"Satisfactorio",IF(ABS(H36)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E36^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2))),SQRT(E36^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2)=0),"",(D36-INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))/SQRT(E36^2+INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="str">
+        <f aca="false">IF(J36="","N/A",IF(ABS(J36)&lt;=2,"Satisfactorio",IF(ABS(J36)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E36)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0)))^2))),SQRT((2*E36)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0)))^2)=0),"",(D36-INDEX(valor_asignado!$C:$C,MATCH(B36,valor_asignado!$B:$B,0)))/SQRT((2*E36)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B36,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="str">
+        <f aca="false">IF(L36="","N/A",IF(ABS(L36)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N36" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D36="",validacion_snapshot!$U$83=""),0,IFERROR(ABS(D36-validacion_snapshot!$U$83),1E+099)),IF(AND(E36="",validacion_snapshot!$V$83=""),0,IFERROR(ABS(E36-validacion_snapshot!$V$83),1E+099)),IF(AND(F36="",validacion_snapshot!$W$83=""),0,IFERROR(ABS(F36-validacion_snapshot!$W$83),1E+099)),IF(AND(H36="",validacion_snapshot!$Y$83=""),0,IFERROR(ABS(H36-validacion_snapshot!$Y$83),1E+099)),IF(AND(J36="",validacion_snapshot!$AA$83=""),0,IFERROR(ABS(J36-validacion_snapshot!$AA$83),1E+099)),IF(AND(L36="",validacion_snapshot!$AC$83=""),0,IFERROR(ABS(L36-validacion_snapshot!$AC$83),1E+099)))&lt;=0.00000001,G36=validacion_snapshot!$X$83,I36=validacion_snapshot!$Z$83,K36=validacion_snapshot!$AB$83,M36=validacion_snapshot!$AD$83),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C37,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C37,datos_participantes!$A:$A,0))</f>
+        <v>1.16255943695127E-005</v>
+      </c>
+      <c r="F37" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0))=0),"",(D37-INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G37" s="5" t="str">
+        <f aca="false">IF(F37="","N/A",IF(ABS(F37)&lt;=2,"Satisfactorio",IF(ABS(F37)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H37" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2)=0),"",(D37-INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B37,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I37" s="5" t="str">
+        <f aca="false">IF(H37="","N/A",IF(ABS(H37)&lt;=2,"Satisfactorio",IF(ABS(H37)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E37^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2))),SQRT(E37^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2)=0),"",(D37-INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))/SQRT(E37^2+INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="str">
+        <f aca="false">IF(J37="","N/A",IF(ABS(J37)&lt;=2,"Satisfactorio",IF(ABS(J37)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E37)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0)))^2))),SQRT((2*E37)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0)))^2)=0),"",(D37-INDEX(valor_asignado!$C:$C,MATCH(B37,valor_asignado!$B:$B,0)))/SQRT((2*E37)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B37,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="str">
+        <f aca="false">IF(L37="","N/A",IF(ABS(L37)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N37" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D37="",validacion_snapshot!$U$84=""),0,IFERROR(ABS(D37-validacion_snapshot!$U$84),1E+099)),IF(AND(E37="",validacion_snapshot!$V$84=""),0,IFERROR(ABS(E37-validacion_snapshot!$V$84),1E+099)),IF(AND(F37="",validacion_snapshot!$W$84=""),0,IFERROR(ABS(F37-validacion_snapshot!$W$84),1E+099)),IF(AND(H37="",validacion_snapshot!$Y$84=""),0,IFERROR(ABS(H37-validacion_snapshot!$Y$84),1E+099)),IF(AND(J37="",validacion_snapshot!$AA$84=""),0,IFERROR(ABS(J37-validacion_snapshot!$AA$84),1E+099)),IF(AND(L37="",validacion_snapshot!$AC$84=""),0,IFERROR(ABS(L37-validacion_snapshot!$AC$84),1E+099)))&lt;=0.00000001,G37=validacion_snapshot!$X$84,I37=validacion_snapshot!$Z$84,K37=validacion_snapshot!$AB$84,M37=validacion_snapshot!$AD$84),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C38,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C38,datos_participantes!$A:$A,0))</f>
+        <v>5.36666666666667E-006</v>
+      </c>
+      <c r="F38" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D38)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0))=0),"",(D38-INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G38" s="5" t="str">
+        <f aca="false">IF(F38="","N/A",IF(ABS(F38)&lt;=2,"Satisfactorio",IF(ABS(F38)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H38" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D38)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2)=0),"",(D38-INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B38,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I38" s="5" t="str">
+        <f aca="false">IF(H38="","N/A",IF(ABS(H38)&lt;=2,"Satisfactorio",IF(ABS(H38)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D38)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E38^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2))),SQRT(E38^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2)=0),"",(D38-INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))/SQRT(E38^2+INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="str">
+        <f aca="false">IF(J38="","N/A",IF(ABS(J38)&lt;=2,"Satisfactorio",IF(ABS(J38)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D38)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E38)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0)))^2))),SQRT((2*E38)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0)))^2)=0),"",(D38-INDEX(valor_asignado!$C:$C,MATCH(B38,valor_asignado!$B:$B,0)))/SQRT((2*E38)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B38,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="str">
+        <f aca="false">IF(L38="","N/A",IF(ABS(L38)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N38" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D38="",validacion_snapshot!$U$85=""),0,IFERROR(ABS(D38-validacion_snapshot!$U$85),1E+099)),IF(AND(E38="",validacion_snapshot!$V$85=""),0,IFERROR(ABS(E38-validacion_snapshot!$V$85),1E+099)),IF(AND(F38="",validacion_snapshot!$W$85=""),0,IFERROR(ABS(F38-validacion_snapshot!$W$85),1E+099)),IF(AND(H38="",validacion_snapshot!$Y$85=""),0,IFERROR(ABS(H38-validacion_snapshot!$Y$85),1E+099)),IF(AND(J38="",validacion_snapshot!$AA$85=""),0,IFERROR(ABS(J38-validacion_snapshot!$AA$85),1E+099)),IF(AND(L38="",validacion_snapshot!$AC$85=""),0,IFERROR(ABS(L38-validacion_snapshot!$AC$85),1E+099)))&lt;=0.00000001,G38=validacion_snapshot!$X$85,I38=validacion_snapshot!$Z$85,K38=validacion_snapshot!$AB$85,M38=validacion_snapshot!$AD$85),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C39,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C39,datos_participantes!$A:$A,0))</f>
+        <v>1.8475208614068E-006</v>
+      </c>
+      <c r="F39" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D39)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0))=0),"",(D39-INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G39" s="5" t="str">
+        <f aca="false">IF(F39="","N/A",IF(ABS(F39)&lt;=2,"Satisfactorio",IF(ABS(F39)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H39" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D39)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2)=0),"",(D39-INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B39,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I39" s="5" t="str">
+        <f aca="false">IF(H39="","N/A",IF(ABS(H39)&lt;=2,"Satisfactorio",IF(ABS(H39)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D39)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E39^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2))),SQRT(E39^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2)=0),"",(D39-INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))/SQRT(E39^2+INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="str">
+        <f aca="false">IF(J39="","N/A",IF(ABS(J39)&lt;=2,"Satisfactorio",IF(ABS(J39)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D39)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E39)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0)))^2))),SQRT((2*E39)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0)))^2)=0),"",(D39-INDEX(valor_asignado!$C:$C,MATCH(B39,valor_asignado!$B:$B,0)))/SQRT((2*E39)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B39,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="str">
+        <f aca="false">IF(L39="","N/A",IF(ABS(L39)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N39" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D39="",validacion_snapshot!$U$86=""),0,IFERROR(ABS(D39-validacion_snapshot!$U$86),1E+099)),IF(AND(E39="",validacion_snapshot!$V$86=""),0,IFERROR(ABS(E39-validacion_snapshot!$V$86),1E+099)),IF(AND(F39="",validacion_snapshot!$W$86=""),0,IFERROR(ABS(F39-validacion_snapshot!$W$86),1E+099)),IF(AND(H39="",validacion_snapshot!$Y$86=""),0,IFERROR(ABS(H39-validacion_snapshot!$Y$86),1E+099)),IF(AND(J39="",validacion_snapshot!$AA$86=""),0,IFERROR(ABS(J39-validacion_snapshot!$AA$86),1E+099)),IF(AND(L39="",validacion_snapshot!$AC$86=""),0,IFERROR(ABS(L39-validacion_snapshot!$AC$86),1E+099)))&lt;=0.00000001,G39=validacion_snapshot!$X$86,I39=validacion_snapshot!$Z$86,K39=validacion_snapshot!$AB$86,M39=validacion_snapshot!$AD$86),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C40,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C40,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F40" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D40)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0))=0),"",(D40-INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G40" s="5" t="str">
+        <f aca="false">IF(F40="","N/A",IF(ABS(F40)&lt;=2,"Satisfactorio",IF(ABS(F40)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H40" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D40)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2)=0),"",(D40-INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B40,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I40" s="5" t="str">
+        <f aca="false">IF(H40="","N/A",IF(ABS(H40)&lt;=2,"Satisfactorio",IF(ABS(H40)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D40)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E40^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2))),SQRT(E40^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2)=0),"",(D40-INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))/SQRT(E40^2+INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="str">
+        <f aca="false">IF(J40="","N/A",IF(ABS(J40)&lt;=2,"Satisfactorio",IF(ABS(J40)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D40)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E40)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0)))^2))),SQRT((2*E40)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0)))^2)=0),"",(D40-INDEX(valor_asignado!$C:$C,MATCH(B40,valor_asignado!$B:$B,0)))/SQRT((2*E40)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B40,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="str">
+        <f aca="false">IF(L40="","N/A",IF(ABS(L40)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N40" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D40="",validacion_snapshot!$U$87=""),0,IFERROR(ABS(D40-validacion_snapshot!$U$87),1E+099)),IF(AND(E40="",validacion_snapshot!$V$87=""),0,IFERROR(ABS(E40-validacion_snapshot!$V$87),1E+099)),IF(AND(F40="",validacion_snapshot!$W$87=""),0,IFERROR(ABS(F40-validacion_snapshot!$W$87),1E+099)),IF(AND(H40="",validacion_snapshot!$Y$87=""),0,IFERROR(ABS(H40-validacion_snapshot!$Y$87),1E+099)),IF(AND(J40="",validacion_snapshot!$AA$87=""),0,IFERROR(ABS(J40-validacion_snapshot!$AA$87),1E+099)),IF(AND(L40="",validacion_snapshot!$AC$87=""),0,IFERROR(ABS(L40-validacion_snapshot!$AC$87),1E+099)))&lt;=0.00000001,G40=validacion_snapshot!$X$87,I40=validacion_snapshot!$Z$87,K40=validacion_snapshot!$AB$87,M40=validacion_snapshot!$AD$87),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C41,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C41,datos_participantes!$A:$A,0))</f>
+        <v>6.69336321374473E-006</v>
+      </c>
+      <c r="F41" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D41)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0))=0),"",(D41-INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G41" s="5" t="str">
+        <f aca="false">IF(F41="","N/A",IF(ABS(F41)&lt;=2,"Satisfactorio",IF(ABS(F41)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H41" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D41)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2)=0),"",(D41-INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B41,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I41" s="5" t="str">
+        <f aca="false">IF(H41="","N/A",IF(ABS(H41)&lt;=2,"Satisfactorio",IF(ABS(H41)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D41)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E41^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2))),SQRT(E41^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2)=0),"",(D41-INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))/SQRT(E41^2+INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="str">
+        <f aca="false">IF(J41="","N/A",IF(ABS(J41)&lt;=2,"Satisfactorio",IF(ABS(J41)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D41)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E41)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0)))^2))),SQRT((2*E41)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0)))^2)=0),"",(D41-INDEX(valor_asignado!$C:$C,MATCH(B41,valor_asignado!$B:$B,0)))/SQRT((2*E41)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B41,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="str">
+        <f aca="false">IF(L41="","N/A",IF(ABS(L41)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N41" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D41="",validacion_snapshot!$U$88=""),0,IFERROR(ABS(D41-validacion_snapshot!$U$88),1E+099)),IF(AND(E41="",validacion_snapshot!$V$88=""),0,IFERROR(ABS(E41-validacion_snapshot!$V$88),1E+099)),IF(AND(F41="",validacion_snapshot!$W$88=""),0,IFERROR(ABS(F41-validacion_snapshot!$W$88),1E+099)),IF(AND(H41="",validacion_snapshot!$Y$88=""),0,IFERROR(ABS(H41-validacion_snapshot!$Y$88),1E+099)),IF(AND(J41="",validacion_snapshot!$AA$88=""),0,IFERROR(ABS(J41-validacion_snapshot!$AA$88),1E+099)),IF(AND(L41="",validacion_snapshot!$AC$88=""),0,IFERROR(ABS(L41-validacion_snapshot!$AC$88),1E+099)))&lt;=0.00000001,G41=validacion_snapshot!$X$88,I41=validacion_snapshot!$Z$88,K41=validacion_snapshot!$AB$88,M41=validacion_snapshot!$AD$88),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C42,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C42,datos_participantes!$A:$A,0))</f>
+        <v>5.67577699037272E-006</v>
+      </c>
+      <c r="F42" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D42)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0))=0),"",(D42-INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G42" s="5" t="str">
+        <f aca="false">IF(F42="","N/A",IF(ABS(F42)&lt;=2,"Satisfactorio",IF(ABS(F42)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D42)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2)=0),"",(D42-INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B42,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I42" s="5" t="str">
+        <f aca="false">IF(H42="","N/A",IF(ABS(H42)&lt;=2,"Satisfactorio",IF(ABS(H42)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D42)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E42^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2))),SQRT(E42^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2)=0),"",(D42-INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))/SQRT(E42^2+INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="str">
+        <f aca="false">IF(J42="","N/A",IF(ABS(J42)&lt;=2,"Satisfactorio",IF(ABS(J42)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D42)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E42)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0)))^2))),SQRT((2*E42)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0)))^2)=0),"",(D42-INDEX(valor_asignado!$C:$C,MATCH(B42,valor_asignado!$B:$B,0)))/SQRT((2*E42)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B42,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="str">
+        <f aca="false">IF(L42="","N/A",IF(ABS(L42)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N42" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D42="",validacion_snapshot!$U$89=""),0,IFERROR(ABS(D42-validacion_snapshot!$U$89),1E+099)),IF(AND(E42="",validacion_snapshot!$V$89=""),0,IFERROR(ABS(E42-validacion_snapshot!$V$89),1E+099)),IF(AND(F42="",validacion_snapshot!$W$89=""),0,IFERROR(ABS(F42-validacion_snapshot!$W$89),1E+099)),IF(AND(H42="",validacion_snapshot!$Y$89=""),0,IFERROR(ABS(H42-validacion_snapshot!$Y$89),1E+099)),IF(AND(J42="",validacion_snapshot!$AA$89=""),0,IFERROR(ABS(J42-validacion_snapshot!$AA$89),1E+099)),IF(AND(L42="",validacion_snapshot!$AC$89=""),0,IFERROR(ABS(L42-validacion_snapshot!$AC$89),1E+099)))&lt;=0.00000001,G42=validacion_snapshot!$X$89,I42=validacion_snapshot!$Z$89,K42=validacion_snapshot!$AB$89,M42=validacion_snapshot!$AD$89),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C43,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C43,datos_participantes!$A:$A,0))</f>
+        <v>1.06666666666667E-006</v>
+      </c>
+      <c r="F43" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D43)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0))=0),"",(D43-INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G43" s="5" t="str">
+        <f aca="false">IF(F43="","N/A",IF(ABS(F43)&lt;=2,"Satisfactorio",IF(ABS(F43)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H43" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D43)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2)=0),"",(D43-INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B43,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I43" s="5" t="str">
+        <f aca="false">IF(H43="","N/A",IF(ABS(H43)&lt;=2,"Satisfactorio",IF(ABS(H43)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D43)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E43^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2))),SQRT(E43^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2)=0),"",(D43-INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))/SQRT(E43^2+INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="str">
+        <f aca="false">IF(J43="","N/A",IF(ABS(J43)&lt;=2,"Satisfactorio",IF(ABS(J43)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D43)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E43)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0)))^2))),SQRT((2*E43)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0)))^2)=0),"",(D43-INDEX(valor_asignado!$C:$C,MATCH(B43,valor_asignado!$B:$B,0)))/SQRT((2*E43)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B43,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="str">
+        <f aca="false">IF(L43="","N/A",IF(ABS(L43)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N43" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D43="",validacion_snapshot!$U$90=""),0,IFERROR(ABS(D43-validacion_snapshot!$U$90),1E+099)),IF(AND(E43="",validacion_snapshot!$V$90=""),0,IFERROR(ABS(E43-validacion_snapshot!$V$90),1E+099)),IF(AND(F43="",validacion_snapshot!$W$90=""),0,IFERROR(ABS(F43-validacion_snapshot!$W$90),1E+099)),IF(AND(H43="",validacion_snapshot!$Y$90=""),0,IFERROR(ABS(H43-validacion_snapshot!$Y$90),1E+099)),IF(AND(J43="",validacion_snapshot!$AA$90=""),0,IFERROR(ABS(J43-validacion_snapshot!$AA$90),1E+099)),IF(AND(L43="",validacion_snapshot!$AC$90=""),0,IFERROR(ABS(L43-validacion_snapshot!$AC$90),1E+099)))&lt;=0.00000001,G43=validacion_snapshot!$X$90,I43=validacion_snapshot!$Z$90,K43=validacion_snapshot!$AB$90,M43=validacion_snapshot!$AD$90),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C44,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C44,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F44" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D44)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0))=0),"",(D44-INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G44" s="5" t="str">
+        <f aca="false">IF(F44="","N/A",IF(ABS(F44)&lt;=2,"Satisfactorio",IF(ABS(F44)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H44" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D44)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2)=0),"",(D44-INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B44,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I44" s="5" t="str">
+        <f aca="false">IF(H44="","N/A",IF(ABS(H44)&lt;=2,"Satisfactorio",IF(ABS(H44)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D44)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E44^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2))),SQRT(E44^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2)=0),"",(D44-INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))/SQRT(E44^2+INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="str">
+        <f aca="false">IF(J44="","N/A",IF(ABS(J44)&lt;=2,"Satisfactorio",IF(ABS(J44)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D44)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E44)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0)))^2))),SQRT((2*E44)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0)))^2)=0),"",(D44-INDEX(valor_asignado!$C:$C,MATCH(B44,valor_asignado!$B:$B,0)))/SQRT((2*E44)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B44,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="str">
+        <f aca="false">IF(L44="","N/A",IF(ABS(L44)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N44" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D44="",validacion_snapshot!$U$91=""),0,IFERROR(ABS(D44-validacion_snapshot!$U$91),1E+099)),IF(AND(E44="",validacion_snapshot!$V$91=""),0,IFERROR(ABS(E44-validacion_snapshot!$V$91),1E+099)),IF(AND(F44="",validacion_snapshot!$W$91=""),0,IFERROR(ABS(F44-validacion_snapshot!$W$91),1E+099)),IF(AND(H44="",validacion_snapshot!$Y$91=""),0,IFERROR(ABS(H44-validacion_snapshot!$Y$91),1E+099)),IF(AND(J44="",validacion_snapshot!$AA$91=""),0,IFERROR(ABS(J44-validacion_snapshot!$AA$91),1E+099)),IF(AND(L44="",validacion_snapshot!$AC$91=""),0,IFERROR(ABS(L44-validacion_snapshot!$AC$91),1E+099)))&lt;=0.00000001,G44=validacion_snapshot!$X$91,I44=validacion_snapshot!$Z$91,K44=validacion_snapshot!$AB$91,M44=validacion_snapshot!$AD$91),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C45,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C45,datos_participantes!$A:$A,0))</f>
+        <v>7.44781847254617E-006</v>
+      </c>
+      <c r="F45" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D45)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0))=0),"",(D45-INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G45" s="5" t="str">
+        <f aca="false">IF(F45="","N/A",IF(ABS(F45)&lt;=2,"Satisfactorio",IF(ABS(F45)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H45" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D45)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2)=0),"",(D45-INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B45,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I45" s="5" t="str">
+        <f aca="false">IF(H45="","N/A",IF(ABS(H45)&lt;=2,"Satisfactorio",IF(ABS(H45)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D45)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E45^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2))),SQRT(E45^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2)=0),"",(D45-INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))/SQRT(E45^2+INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="str">
+        <f aca="false">IF(J45="","N/A",IF(ABS(J45)&lt;=2,"Satisfactorio",IF(ABS(J45)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D45)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E45)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0)))^2))),SQRT((2*E45)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0)))^2)=0),"",(D45-INDEX(valor_asignado!$C:$C,MATCH(B45,valor_asignado!$B:$B,0)))/SQRT((2*E45)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B45,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="str">
+        <f aca="false">IF(L45="","N/A",IF(ABS(L45)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N45" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D45="",validacion_snapshot!$U$92=""),0,IFERROR(ABS(D45-validacion_snapshot!$U$92),1E+099)),IF(AND(E45="",validacion_snapshot!$V$92=""),0,IFERROR(ABS(E45-validacion_snapshot!$V$92),1E+099)),IF(AND(F45="",validacion_snapshot!$W$92=""),0,IFERROR(ABS(F45-validacion_snapshot!$W$92),1E+099)),IF(AND(H45="",validacion_snapshot!$Y$92=""),0,IFERROR(ABS(H45-validacion_snapshot!$Y$92),1E+099)),IF(AND(J45="",validacion_snapshot!$AA$92=""),0,IFERROR(ABS(J45-validacion_snapshot!$AA$92),1E+099)),IF(AND(L45="",validacion_snapshot!$AC$92=""),0,IFERROR(ABS(L45-validacion_snapshot!$AC$92),1E+099)))&lt;=0.00000001,G45=validacion_snapshot!$X$92,I45=validacion_snapshot!$Z$92,K45=validacion_snapshot!$AB$92,M45=validacion_snapshot!$AD$92),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C46,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C46,datos_participantes!$A:$A,0))</f>
+        <v>2.84741598256696E-006</v>
+      </c>
+      <c r="F46" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D46)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0))=0),"",(D46-INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G46" s="5" t="str">
+        <f aca="false">IF(F46="","N/A",IF(ABS(F46)&lt;=2,"Satisfactorio",IF(ABS(F46)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H46" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D46)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2)=0),"",(D46-INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B46,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I46" s="5" t="str">
+        <f aca="false">IF(H46="","N/A",IF(ABS(H46)&lt;=2,"Satisfactorio",IF(ABS(H46)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D46)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E46^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2))),SQRT(E46^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2)=0),"",(D46-INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))/SQRT(E46^2+INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="str">
+        <f aca="false">IF(J46="","N/A",IF(ABS(J46)&lt;=2,"Satisfactorio",IF(ABS(J46)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D46)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E46)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0)))^2))),SQRT((2*E46)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0)))^2)=0),"",(D46-INDEX(valor_asignado!$C:$C,MATCH(B46,valor_asignado!$B:$B,0)))/SQRT((2*E46)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B46,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="str">
+        <f aca="false">IF(L46="","N/A",IF(ABS(L46)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N46" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D46="",validacion_snapshot!$U$93=""),0,IFERROR(ABS(D46-validacion_snapshot!$U$93),1E+099)),IF(AND(E46="",validacion_snapshot!$V$93=""),0,IFERROR(ABS(E46-validacion_snapshot!$V$93),1E+099)),IF(AND(F46="",validacion_snapshot!$W$93=""),0,IFERROR(ABS(F46-validacion_snapshot!$W$93),1E+099)),IF(AND(H46="",validacion_snapshot!$Y$93=""),0,IFERROR(ABS(H46-validacion_snapshot!$Y$93),1E+099)),IF(AND(J46="",validacion_snapshot!$AA$93=""),0,IFERROR(ABS(J46-validacion_snapshot!$AA$93),1E+099)),IF(AND(L46="",validacion_snapshot!$AC$93=""),0,IFERROR(ABS(L46-validacion_snapshot!$AC$93),1E+099)))&lt;=0.00000001,G46=validacion_snapshot!$X$93,I46=validacion_snapshot!$Z$93,K46=validacion_snapshot!$AB$93,M46=validacion_snapshot!$AD$93),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C47,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C47,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F47" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D47)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0))=0),"",(D47-INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G47" s="5" t="str">
+        <f aca="false">IF(F47="","N/A",IF(ABS(F47)&lt;=2,"Satisfactorio",IF(ABS(F47)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H47" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D47)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2)=0),"",(D47-INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B47,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I47" s="5" t="str">
+        <f aca="false">IF(H47="","N/A",IF(ABS(H47)&lt;=2,"Satisfactorio",IF(ABS(H47)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D47)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E47^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2))),SQRT(E47^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2)=0),"",(D47-INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))/SQRT(E47^2+INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="5" t="str">
+        <f aca="false">IF(J47="","N/A",IF(ABS(J47)&lt;=2,"Satisfactorio",IF(ABS(J47)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D47)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E47)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0)))^2))),SQRT((2*E47)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0)))^2)=0),"",(D47-INDEX(valor_asignado!$C:$C,MATCH(B47,valor_asignado!$B:$B,0)))/SQRT((2*E47)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B47,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="str">
+        <f aca="false">IF(L47="","N/A",IF(ABS(L47)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N47" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D47="",validacion_snapshot!$U$94=""),0,IFERROR(ABS(D47-validacion_snapshot!$U$94),1E+099)),IF(AND(E47="",validacion_snapshot!$V$94=""),0,IFERROR(ABS(E47-validacion_snapshot!$V$94),1E+099)),IF(AND(F47="",validacion_snapshot!$W$94=""),0,IFERROR(ABS(F47-validacion_snapshot!$W$94),1E+099)),IF(AND(H47="",validacion_snapshot!$Y$94=""),0,IFERROR(ABS(H47-validacion_snapshot!$Y$94),1E+099)),IF(AND(J47="",validacion_snapshot!$AA$94=""),0,IFERROR(ABS(J47-validacion_snapshot!$AA$94),1E+099)),IF(AND(L47="",validacion_snapshot!$AC$94=""),0,IFERROR(ABS(L47-validacion_snapshot!$AC$94),1E+099)))&lt;=0.00000001,G47=validacion_snapshot!$X$94,I47=validacion_snapshot!$Z$94,K47=validacion_snapshot!$AB$94,M47=validacion_snapshot!$AD$94),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C48,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C48,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F48" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D48)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0))=0),"",(D48-INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G48" s="5" t="str">
+        <f aca="false">IF(F48="","N/A",IF(ABS(F48)&lt;=2,"Satisfactorio",IF(ABS(F48)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H48" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D48)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2)=0),"",(D48-INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B48,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I48" s="5" t="str">
+        <f aca="false">IF(H48="","N/A",IF(ABS(H48)&lt;=2,"Satisfactorio",IF(ABS(H48)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D48)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E48^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2))),SQRT(E48^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2)=0),"",(D48-INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))/SQRT(E48^2+INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="str">
+        <f aca="false">IF(J48="","N/A",IF(ABS(J48)&lt;=2,"Satisfactorio",IF(ABS(J48)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D48)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E48)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0)))^2))),SQRT((2*E48)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0)))^2)=0),"",(D48-INDEX(valor_asignado!$C:$C,MATCH(B48,valor_asignado!$B:$B,0)))/SQRT((2*E48)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B48,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="str">
+        <f aca="false">IF(L48="","N/A",IF(ABS(L48)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N48" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D48="",validacion_snapshot!$U$95=""),0,IFERROR(ABS(D48-validacion_snapshot!$U$95),1E+099)),IF(AND(E48="",validacion_snapshot!$V$95=""),0,IFERROR(ABS(E48-validacion_snapshot!$V$95),1E+099)),IF(AND(F48="",validacion_snapshot!$W$95=""),0,IFERROR(ABS(F48-validacion_snapshot!$W$95),1E+099)),IF(AND(H48="",validacion_snapshot!$Y$95=""),0,IFERROR(ABS(H48-validacion_snapshot!$Y$95),1E+099)),IF(AND(J48="",validacion_snapshot!$AA$95=""),0,IFERROR(ABS(J48-validacion_snapshot!$AA$95),1E+099)),IF(AND(L48="",validacion_snapshot!$AC$95=""),0,IFERROR(ABS(L48-validacion_snapshot!$AC$95),1E+099)))&lt;=0.00000001,G48=validacion_snapshot!$X$95,I48=validacion_snapshot!$Z$95,K48=validacion_snapshot!$AB$95,M48=validacion_snapshot!$AD$95),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C49,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C49,datos_participantes!$A:$A,0))</f>
+        <v>1.16255943695127E-005</v>
+      </c>
+      <c r="F49" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D49)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0))=0),"",(D49-INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0)))</f>
+        <v/>
+      </c>
+      <c r="G49" s="5" t="str">
+        <f aca="false">IF(F49="","N/A",IF(ABS(F49)&lt;=2,"Satisfactorio",IF(ABS(F49)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="H49" s="4" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D49)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2)=0),"",(D49-INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B49,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2))</f>
+        <v/>
+      </c>
+      <c r="I49" s="5" t="str">
+        <f aca="false">IF(H49="","N/A",IF(ABS(H49)&lt;=2,"Satisfactorio",IF(ABS(H49)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D49)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E49^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2))),SQRT(E49^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2)=0),"",(D49-INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))/SQRT(E49^2+INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="5" t="str">
+        <f aca="false">IF(J49="","N/A",IF(ABS(J49)&lt;=2,"Satisfactorio",IF(ABS(J49)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D49)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E49)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0)))^2))),SQRT((2*E49)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0)))^2)=0),"",(D49-INDEX(valor_asignado!$C:$C,MATCH(B49,valor_asignado!$B:$B,0)))/SQRT((2*E49)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B49,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="str">
+        <f aca="false">IF(L49="","N/A",IF(ABS(L49)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N49" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D49="",validacion_snapshot!$U$96=""),0,IFERROR(ABS(D49-validacion_snapshot!$U$96),1E+099)),IF(AND(E49="",validacion_snapshot!$V$96=""),0,IFERROR(ABS(E49-validacion_snapshot!$V$96),1E+099)),IF(AND(F49="",validacion_snapshot!$W$96=""),0,IFERROR(ABS(F49-validacion_snapshot!$W$96),1E+099)),IF(AND(H49="",validacion_snapshot!$Y$96=""),0,IFERROR(ABS(H49-validacion_snapshot!$Y$96),1E+099)),IF(AND(J49="",validacion_snapshot!$AA$96=""),0,IFERROR(ABS(J49-validacion_snapshot!$AA$96),1E+099)),IF(AND(L49="",validacion_snapshot!$AC$96=""),0,IFERROR(ABS(L49-validacion_snapshot!$AC$96),1E+099)))&lt;=0.00000001,G49=validacion_snapshot!$X$96,I49=validacion_snapshot!$Z$96,K49=validacion_snapshot!$AB$96,M49=validacion_snapshot!$AD$96),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C50,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C50,datos_participantes!$A:$A,0))</f>
+        <v>5.36666666666667E-006</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D50)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0))=0),"",(D50-INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="str">
+        <f aca="false">IF(F50="","N/A",IF(ABS(F50)&lt;=2,"Satisfactorio",IF(ABS(F50)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D50)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2)=0),"",(D50-INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B50,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="str">
+        <f aca="false">IF(H50="","N/A",IF(ABS(H50)&lt;=2,"Satisfactorio",IF(ABS(H50)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D50)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E50^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2))),SQRT(E50^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2)=0),"",(D50-INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))/SQRT(E50^2+INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="str">
+        <f aca="false">IF(J50="","N/A",IF(ABS(J50)&lt;=2,"Satisfactorio",IF(ABS(J50)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D50)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E50)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0)))^2))),SQRT((2*E50)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0)))^2)=0),"",(D50-INDEX(valor_asignado!$C:$C,MATCH(B50,valor_asignado!$B:$B,0)))/SQRT((2*E50)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B50,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="str">
+        <f aca="false">IF(L50="","N/A",IF(ABS(L50)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N50" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D50="",validacion_snapshot!$U$97=""),0,IFERROR(ABS(D50-validacion_snapshot!$U$97),1E+099)),IF(AND(E50="",validacion_snapshot!$V$97=""),0,IFERROR(ABS(E50-validacion_snapshot!$V$97),1E+099)),IF(AND(F50="",validacion_snapshot!$W$97=""),0,IFERROR(ABS(F50-validacion_snapshot!$W$97),1E+099)),IF(AND(H50="",validacion_snapshot!$Y$97=""),0,IFERROR(ABS(H50-validacion_snapshot!$Y$97),1E+099)),IF(AND(J50="",validacion_snapshot!$AA$97=""),0,IFERROR(ABS(J50-validacion_snapshot!$AA$97),1E+099)),IF(AND(L50="",validacion_snapshot!$AC$97=""),0,IFERROR(ABS(L50-validacion_snapshot!$AC$97),1E+099)))&lt;=0.00000001,G50=validacion_snapshot!$X$97,I50=validacion_snapshot!$Z$97,K50=validacion_snapshot!$AB$97,M50=validacion_snapshot!$AD$97),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C51,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C51,datos_participantes!$A:$A,0))</f>
+        <v>1.8475208614068E-006</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D51)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0))=0),"",(D51-INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="str">
+        <f aca="false">IF(F51="","N/A",IF(ABS(F51)&lt;=2,"Satisfactorio",IF(ABS(F51)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D51)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2)=0),"",(D51-INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B51,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="str">
+        <f aca="false">IF(H51="","N/A",IF(ABS(H51)&lt;=2,"Satisfactorio",IF(ABS(H51)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D51)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E51^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2))),SQRT(E51^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2)=0),"",(D51-INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))/SQRT(E51^2+INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="5" t="str">
+        <f aca="false">IF(J51="","N/A",IF(ABS(J51)&lt;=2,"Satisfactorio",IF(ABS(J51)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D51)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E51)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0)))^2))),SQRT((2*E51)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0)))^2)=0),"",(D51-INDEX(valor_asignado!$C:$C,MATCH(B51,valor_asignado!$B:$B,0)))/SQRT((2*E51)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B51,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="5" t="str">
+        <f aca="false">IF(L51="","N/A",IF(ABS(L51)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N51" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D51="",validacion_snapshot!$U$98=""),0,IFERROR(ABS(D51-validacion_snapshot!$U$98),1E+099)),IF(AND(E51="",validacion_snapshot!$V$98=""),0,IFERROR(ABS(E51-validacion_snapshot!$V$98),1E+099)),IF(AND(F51="",validacion_snapshot!$W$98=""),0,IFERROR(ABS(F51-validacion_snapshot!$W$98),1E+099)),IF(AND(H51="",validacion_snapshot!$Y$98=""),0,IFERROR(ABS(H51-validacion_snapshot!$Y$98),1E+099)),IF(AND(J51="",validacion_snapshot!$AA$98=""),0,IFERROR(ABS(J51-validacion_snapshot!$AA$98),1E+099)),IF(AND(L51="",validacion_snapshot!$AC$98=""),0,IFERROR(ABS(L51-validacion_snapshot!$AC$98),1E+099)))&lt;=0.00000001,G51=validacion_snapshot!$X$98,I51=validacion_snapshot!$Z$98,K51=validacion_snapshot!$AB$98,M51=validacion_snapshot!$AD$98),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C52,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C52,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D52)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0))=0),"",(D52-INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="str">
+        <f aca="false">IF(F52="","N/A",IF(ABS(F52)&lt;=2,"Satisfactorio",IF(ABS(F52)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D52)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2)=0),"",(D52-INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B52,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="str">
+        <f aca="false">IF(H52="","N/A",IF(ABS(H52)&lt;=2,"Satisfactorio",IF(ABS(H52)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D52)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E52^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2))),SQRT(E52^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2)=0),"",(D52-INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))/SQRT(E52^2+INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="str">
+        <f aca="false">IF(J52="","N/A",IF(ABS(J52)&lt;=2,"Satisfactorio",IF(ABS(J52)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D52)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E52)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0)))^2))),SQRT((2*E52)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0)))^2)=0),"",(D52-INDEX(valor_asignado!$C:$C,MATCH(B52,valor_asignado!$B:$B,0)))/SQRT((2*E52)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B52,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="str">
+        <f aca="false">IF(L52="","N/A",IF(ABS(L52)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N52" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D52="",validacion_snapshot!$U$99=""),0,IFERROR(ABS(D52-validacion_snapshot!$U$99),1E+099)),IF(AND(E52="",validacion_snapshot!$V$99=""),0,IFERROR(ABS(E52-validacion_snapshot!$V$99),1E+099)),IF(AND(F52="",validacion_snapshot!$W$99=""),0,IFERROR(ABS(F52-validacion_snapshot!$W$99),1E+099)),IF(AND(H52="",validacion_snapshot!$Y$99=""),0,IFERROR(ABS(H52-validacion_snapshot!$Y$99),1E+099)),IF(AND(J52="",validacion_snapshot!$AA$99=""),0,IFERROR(ABS(J52-validacion_snapshot!$AA$99),1E+099)),IF(AND(L52="",validacion_snapshot!$AC$99=""),0,IFERROR(ABS(L52-validacion_snapshot!$AC$99),1E+099)))&lt;=0.00000001,G52=validacion_snapshot!$X$99,I52=validacion_snapshot!$Z$99,K52=validacion_snapshot!$AB$99,M52=validacion_snapshot!$AD$99),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C53,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C53,datos_participantes!$A:$A,0))</f>
+        <v>6.69336321374473E-006</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D53)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0))=0),"",(D53-INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="str">
+        <f aca="false">IF(F53="","N/A",IF(ABS(F53)&lt;=2,"Satisfactorio",IF(ABS(F53)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D53)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2)=0),"",(D53-INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B53,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="str">
+        <f aca="false">IF(H53="","N/A",IF(ABS(H53)&lt;=2,"Satisfactorio",IF(ABS(H53)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D53)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E53^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2))),SQRT(E53^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2)=0),"",(D53-INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))/SQRT(E53^2+INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="5" t="str">
+        <f aca="false">IF(J53="","N/A",IF(ABS(J53)&lt;=2,"Satisfactorio",IF(ABS(J53)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D53)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E53)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0)))^2))),SQRT((2*E53)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0)))^2)=0),"",(D53-INDEX(valor_asignado!$C:$C,MATCH(B53,valor_asignado!$B:$B,0)))/SQRT((2*E53)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B53,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="5" t="str">
+        <f aca="false">IF(L53="","N/A",IF(ABS(L53)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N53" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D53="",validacion_snapshot!$U$100=""),0,IFERROR(ABS(D53-validacion_snapshot!$U$100),1E+099)),IF(AND(E53="",validacion_snapshot!$V$100=""),0,IFERROR(ABS(E53-validacion_snapshot!$V$100),1E+099)),IF(AND(F53="",validacion_snapshot!$W$100=""),0,IFERROR(ABS(F53-validacion_snapshot!$W$100),1E+099)),IF(AND(H53="",validacion_snapshot!$Y$100=""),0,IFERROR(ABS(H53-validacion_snapshot!$Y$100),1E+099)),IF(AND(J53="",validacion_snapshot!$AA$100=""),0,IFERROR(ABS(J53-validacion_snapshot!$AA$100),1E+099)),IF(AND(L53="",validacion_snapshot!$AC$100=""),0,IFERROR(ABS(L53-validacion_snapshot!$AC$100),1E+099)))&lt;=0.00000001,G53=validacion_snapshot!$X$100,I53=validacion_snapshot!$Z$100,K53=validacion_snapshot!$AB$100,M53=validacion_snapshot!$AD$100),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C54,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C54,datos_participantes!$A:$A,0))</f>
+        <v>5.67577699037272E-006</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D54)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0))=0),"",(D54-INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="str">
+        <f aca="false">IF(F54="","N/A",IF(ABS(F54)&lt;=2,"Satisfactorio",IF(ABS(F54)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D54)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2)=0),"",(D54-INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B54,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="str">
+        <f aca="false">IF(H54="","N/A",IF(ABS(H54)&lt;=2,"Satisfactorio",IF(ABS(H54)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D54)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E54^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2))),SQRT(E54^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2)=0),"",(D54-INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))/SQRT(E54^2+INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="str">
+        <f aca="false">IF(J54="","N/A",IF(ABS(J54)&lt;=2,"Satisfactorio",IF(ABS(J54)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D54)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E54)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0)))^2))),SQRT((2*E54)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0)))^2)=0),"",(D54-INDEX(valor_asignado!$C:$C,MATCH(B54,valor_asignado!$B:$B,0)))/SQRT((2*E54)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B54,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="str">
+        <f aca="false">IF(L54="","N/A",IF(ABS(L54)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N54" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D54="",validacion_snapshot!$U$101=""),0,IFERROR(ABS(D54-validacion_snapshot!$U$101),1E+099)),IF(AND(E54="",validacion_snapshot!$V$101=""),0,IFERROR(ABS(E54-validacion_snapshot!$V$101),1E+099)),IF(AND(F54="",validacion_snapshot!$W$101=""),0,IFERROR(ABS(F54-validacion_snapshot!$W$101),1E+099)),IF(AND(H54="",validacion_snapshot!$Y$101=""),0,IFERROR(ABS(H54-validacion_snapshot!$Y$101),1E+099)),IF(AND(J54="",validacion_snapshot!$AA$101=""),0,IFERROR(ABS(J54-validacion_snapshot!$AA$101),1E+099)),IF(AND(L54="",validacion_snapshot!$AC$101=""),0,IFERROR(ABS(L54-validacion_snapshot!$AC$101),1E+099)))&lt;=0.00000001,G54=validacion_snapshot!$X$101,I54=validacion_snapshot!$Z$101,K54=validacion_snapshot!$AB$101,M54=validacion_snapshot!$AD$101),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C55,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C55,datos_participantes!$A:$A,0))</f>
+        <v>1.06666666666667E-006</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D55)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0))=0),"",(D55-INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="str">
+        <f aca="false">IF(F55="","N/A",IF(ABS(F55)&lt;=2,"Satisfactorio",IF(ABS(F55)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D55)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2)=0),"",(D55-INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B55,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="str">
+        <f aca="false">IF(H55="","N/A",IF(ABS(H55)&lt;=2,"Satisfactorio",IF(ABS(H55)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D55)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E55^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2))),SQRT(E55^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2)=0),"",(D55-INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))/SQRT(E55^2+INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="str">
+        <f aca="false">IF(J55="","N/A",IF(ABS(J55)&lt;=2,"Satisfactorio",IF(ABS(J55)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D55)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E55)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0)))^2))),SQRT((2*E55)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0)))^2)=0),"",(D55-INDEX(valor_asignado!$C:$C,MATCH(B55,valor_asignado!$B:$B,0)))/SQRT((2*E55)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B55,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="5" t="str">
+        <f aca="false">IF(L55="","N/A",IF(ABS(L55)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N55" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D55="",validacion_snapshot!$U$102=""),0,IFERROR(ABS(D55-validacion_snapshot!$U$102),1E+099)),IF(AND(E55="",validacion_snapshot!$V$102=""),0,IFERROR(ABS(E55-validacion_snapshot!$V$102),1E+099)),IF(AND(F55="",validacion_snapshot!$W$102=""),0,IFERROR(ABS(F55-validacion_snapshot!$W$102),1E+099)),IF(AND(H55="",validacion_snapshot!$Y$102=""),0,IFERROR(ABS(H55-validacion_snapshot!$Y$102),1E+099)),IF(AND(J55="",validacion_snapshot!$AA$102=""),0,IFERROR(ABS(J55-validacion_snapshot!$AA$102),1E+099)),IF(AND(L55="",validacion_snapshot!$AC$102=""),0,IFERROR(ABS(L55-validacion_snapshot!$AC$102),1E+099)))&lt;=0.00000001,G55=validacion_snapshot!$X$102,I55=validacion_snapshot!$Z$102,K55=validacion_snapshot!$AB$102,M55=validacion_snapshot!$AD$102),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C56,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C56,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D56)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0))=0),"",(D56-INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="str">
+        <f aca="false">IF(F56="","N/A",IF(ABS(F56)&lt;=2,"Satisfactorio",IF(ABS(F56)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D56)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2)=0),"",(D56-INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B56,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="str">
+        <f aca="false">IF(H56="","N/A",IF(ABS(H56)&lt;=2,"Satisfactorio",IF(ABS(H56)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D56)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E56^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2))),SQRT(E56^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2)=0),"",(D56-INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))/SQRT(E56^2+INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="str">
+        <f aca="false">IF(J56="","N/A",IF(ABS(J56)&lt;=2,"Satisfactorio",IF(ABS(J56)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D56)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E56)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0)))^2))),SQRT((2*E56)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0)))^2)=0),"",(D56-INDEX(valor_asignado!$C:$C,MATCH(B56,valor_asignado!$B:$B,0)))/SQRT((2*E56)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B56,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="str">
+        <f aca="false">IF(L56="","N/A",IF(ABS(L56)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N56" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D56="",validacion_snapshot!$U$103=""),0,IFERROR(ABS(D56-validacion_snapshot!$U$103),1E+099)),IF(AND(E56="",validacion_snapshot!$V$103=""),0,IFERROR(ABS(E56-validacion_snapshot!$V$103),1E+099)),IF(AND(F56="",validacion_snapshot!$W$103=""),0,IFERROR(ABS(F56-validacion_snapshot!$W$103),1E+099)),IF(AND(H56="",validacion_snapshot!$Y$103=""),0,IFERROR(ABS(H56-validacion_snapshot!$Y$103),1E+099)),IF(AND(J56="",validacion_snapshot!$AA$103=""),0,IFERROR(ABS(J56-validacion_snapshot!$AA$103),1E+099)),IF(AND(L56="",validacion_snapshot!$AC$103=""),0,IFERROR(ABS(L56-validacion_snapshot!$AC$103),1E+099)))&lt;=0.00000001,G56=validacion_snapshot!$X$103,I56=validacion_snapshot!$Z$103,K56=validacion_snapshot!$AB$103,M56=validacion_snapshot!$AD$103),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C57,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C57,datos_participantes!$A:$A,0))</f>
+        <v>7.44781847254617E-006</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D57)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0))=0),"",(D57-INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="str">
+        <f aca="false">IF(F57="","N/A",IF(ABS(F57)&lt;=2,"Satisfactorio",IF(ABS(F57)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D57)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2)=0),"",(D57-INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B57,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="str">
+        <f aca="false">IF(H57="","N/A",IF(ABS(H57)&lt;=2,"Satisfactorio",IF(ABS(H57)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D57)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E57^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2))),SQRT(E57^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2)=0),"",(D57-INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))/SQRT(E57^2+INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="str">
+        <f aca="false">IF(J57="","N/A",IF(ABS(J57)&lt;=2,"Satisfactorio",IF(ABS(J57)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D57)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E57)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0)))^2))),SQRT((2*E57)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0)))^2)=0),"",(D57-INDEX(valor_asignado!$C:$C,MATCH(B57,valor_asignado!$B:$B,0)))/SQRT((2*E57)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B57,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="5" t="str">
+        <f aca="false">IF(L57="","N/A",IF(ABS(L57)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N57" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D57="",validacion_snapshot!$U$104=""),0,IFERROR(ABS(D57-validacion_snapshot!$U$104),1E+099)),IF(AND(E57="",validacion_snapshot!$V$104=""),0,IFERROR(ABS(E57-validacion_snapshot!$V$104),1E+099)),IF(AND(F57="",validacion_snapshot!$W$104=""),0,IFERROR(ABS(F57-validacion_snapshot!$W$104),1E+099)),IF(AND(H57="",validacion_snapshot!$Y$104=""),0,IFERROR(ABS(H57-validacion_snapshot!$Y$104),1E+099)),IF(AND(J57="",validacion_snapshot!$AA$104=""),0,IFERROR(ABS(J57-validacion_snapshot!$AA$104),1E+099)),IF(AND(L57="",validacion_snapshot!$AC$104=""),0,IFERROR(ABS(L57-validacion_snapshot!$AC$104),1E+099)))&lt;=0.00000001,G57=validacion_snapshot!$X$104,I57=validacion_snapshot!$Z$104,K57=validacion_snapshot!$AB$104,M57=validacion_snapshot!$AD$104),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C58,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C58,datos_participantes!$A:$A,0))</f>
+        <v>2.84741598256696E-006</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D58)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0))=0),"",(D58-INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="str">
+        <f aca="false">IF(F58="","N/A",IF(ABS(F58)&lt;=2,"Satisfactorio",IF(ABS(F58)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D58)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2)=0),"",(D58-INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B58,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="str">
+        <f aca="false">IF(H58="","N/A",IF(ABS(H58)&lt;=2,"Satisfactorio",IF(ABS(H58)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D58)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E58^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2))),SQRT(E58^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2)=0),"",(D58-INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))/SQRT(E58^2+INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="str">
+        <f aca="false">IF(J58="","N/A",IF(ABS(J58)&lt;=2,"Satisfactorio",IF(ABS(J58)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D58)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E58)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0)))^2))),SQRT((2*E58)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0)))^2)=0),"",(D58-INDEX(valor_asignado!$C:$C,MATCH(B58,valor_asignado!$B:$B,0)))/SQRT((2*E58)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B58,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="str">
+        <f aca="false">IF(L58="","N/A",IF(ABS(L58)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N58" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D58="",validacion_snapshot!$U$105=""),0,IFERROR(ABS(D58-validacion_snapshot!$U$105),1E+099)),IF(AND(E58="",validacion_snapshot!$V$105=""),0,IFERROR(ABS(E58-validacion_snapshot!$V$105),1E+099)),IF(AND(F58="",validacion_snapshot!$W$105=""),0,IFERROR(ABS(F58-validacion_snapshot!$W$105),1E+099)),IF(AND(H58="",validacion_snapshot!$Y$105=""),0,IFERROR(ABS(H58-validacion_snapshot!$Y$105),1E+099)),IF(AND(J58="",validacion_snapshot!$AA$105=""),0,IFERROR(ABS(J58-validacion_snapshot!$AA$105),1E+099)),IF(AND(L58="",validacion_snapshot!$AC$105=""),0,IFERROR(ABS(L58-validacion_snapshot!$AC$105),1E+099)))&lt;=0.00000001,G58=validacion_snapshot!$X$105,I58=validacion_snapshot!$Z$105,K58=validacion_snapshot!$AB$105,M58=validacion_snapshot!$AD$105),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C59,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C59,datos_participantes!$A:$A,0))</f>
+        <v>5.97187854308285E-006</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D59)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0))=0),"",(D59-INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="str">
+        <f aca="false">IF(F59="","N/A",IF(ABS(F59)&lt;=2,"Satisfactorio",IF(ABS(F59)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D59)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2)=0),"",(D59-INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B59,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="str">
+        <f aca="false">IF(H59="","N/A",IF(ABS(H59)&lt;=2,"Satisfactorio",IF(ABS(H59)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D59)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E59^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2))),SQRT(E59^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2)=0),"",(D59-INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))/SQRT(E59^2+INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="5" t="str">
+        <f aca="false">IF(J59="","N/A",IF(ABS(J59)&lt;=2,"Satisfactorio",IF(ABS(J59)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D59)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E59)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0)))^2))),SQRT((2*E59)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0)))^2)=0),"",(D59-INDEX(valor_asignado!$C:$C,MATCH(B59,valor_asignado!$B:$B,0)))/SQRT((2*E59)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B59,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="5" t="str">
+        <f aca="false">IF(L59="","N/A",IF(ABS(L59)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N59" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D59="",validacion_snapshot!$U$106=""),0,IFERROR(ABS(D59-validacion_snapshot!$U$106),1E+099)),IF(AND(E59="",validacion_snapshot!$V$106=""),0,IFERROR(ABS(E59-validacion_snapshot!$V$106),1E+099)),IF(AND(F59="",validacion_snapshot!$W$106=""),0,IFERROR(ABS(F59-validacion_snapshot!$W$106),1E+099)),IF(AND(H59="",validacion_snapshot!$Y$106=""),0,IFERROR(ABS(H59-validacion_snapshot!$Y$106),1E+099)),IF(AND(J59="",validacion_snapshot!$AA$106=""),0,IFERROR(ABS(J59-validacion_snapshot!$AA$106),1E+099)),IF(AND(L59="",validacion_snapshot!$AC$106=""),0,IFERROR(ABS(L59-validacion_snapshot!$AC$106),1E+099)))&lt;=0.00000001,G59=validacion_snapshot!$X$106,I59=validacion_snapshot!$Z$106,K59=validacion_snapshot!$AB$106,M59=validacion_snapshot!$AD$106),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C60,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C60,datos_participantes!$A:$A,0))</f>
+        <v>2.85365263010993E-006</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D60)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0))=0),"",(D60-INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="str">
+        <f aca="false">IF(F60="","N/A",IF(ABS(F60)&lt;=2,"Satisfactorio",IF(ABS(F60)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D60)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2)=0),"",(D60-INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B60,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="str">
+        <f aca="false">IF(H60="","N/A",IF(ABS(H60)&lt;=2,"Satisfactorio",IF(ABS(H60)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D60)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E60^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2))),SQRT(E60^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2)=0),"",(D60-INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))/SQRT(E60^2+INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="str">
+        <f aca="false">IF(J60="","N/A",IF(ABS(J60)&lt;=2,"Satisfactorio",IF(ABS(J60)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D60)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E60)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0)))^2))),SQRT((2*E60)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0)))^2)=0),"",(D60-INDEX(valor_asignado!$C:$C,MATCH(B60,valor_asignado!$B:$B,0)))/SQRT((2*E60)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B60,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="str">
+        <f aca="false">IF(L60="","N/A",IF(ABS(L60)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N60" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D60="",validacion_snapshot!$U$107=""),0,IFERROR(ABS(D60-validacion_snapshot!$U$107),1E+099)),IF(AND(E60="",validacion_snapshot!$V$107=""),0,IFERROR(ABS(E60-validacion_snapshot!$V$107),1E+099)),IF(AND(F60="",validacion_snapshot!$W$107=""),0,IFERROR(ABS(F60-validacion_snapshot!$W$107),1E+099)),IF(AND(H60="",validacion_snapshot!$Y$107=""),0,IFERROR(ABS(H60-validacion_snapshot!$Y$107),1E+099)),IF(AND(J60="",validacion_snapshot!$AA$107=""),0,IFERROR(ABS(J60-validacion_snapshot!$AA$107),1E+099)),IF(AND(L60="",validacion_snapshot!$AC$107=""),0,IFERROR(ABS(L60-validacion_snapshot!$AC$107),1E+099)))&lt;=0.00000001,G60=validacion_snapshot!$X$107,I60=validacion_snapshot!$Z$107,K60=validacion_snapshot!$AB$107,M60=validacion_snapshot!$AD$107),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$D:$D,MATCH(C61,datos_participantes!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <f aca="false">INDEX(datos_participantes!$F:$F,MATCH(C61,datos_participantes!$A:$A,0))</f>
+        <v>1.16255943695127E-005</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D61)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0)))),INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0))=0),"",(D61-INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))/INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="str">
+        <f aca="false">IF(F61="","N/A",IF(ABS(F61)&lt;=2,"Satisfactorio",IF(ABS(F61)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D61)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2))),SQRT(INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2)=0),"",(D61-INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))/SQRT(INDEX(valor_asignado!$D:$D,MATCH(B61,valor_asignado!$B:$B,0))^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="str">
+        <f aca="false">IF(H61="","N/A",IF(ABS(H61)&lt;=2,"Satisfactorio",IF(ABS(H61)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D61)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT(E61^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2))),SQRT(E61^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2)=0),"",(D61-INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))/SQRT(E61^2+INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="5" t="str">
+        <f aca="false">IF(J61="","N/A",IF(ABS(J61)&lt;=2,"Satisfactorio",IF(ABS(J61)&lt;3,"Cuestionable","No satisfactorio")))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D61)),NOT(ISNUMBER(INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))),NOT(ISNUMBER(SQRT((2*E61)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0)))^2))),SQRT((2*E61)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0)))^2)=0),"",(D61-INDEX(valor_asignado!$C:$C,MATCH(B61,valor_asignado!$B:$B,0)))/SQRT((2*E61)^2+(2*INDEX(valor_asignado!$H:$H,MATCH(B61,valor_asignado!$B:$B,0)))^2))</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="5" t="str">
+        <f aca="false">IF(L61="","N/A",IF(ABS(L61)&lt;=1,"Satisfactorio","No satisfactorio"))</f>
+        <v>Satisfactorio</v>
+      </c>
+      <c r="N61" s="5" t="str">
+        <f aca="false">IF(AND(SUM(IF(AND(D61="",validacion_snapshot!$U$108=""),0,IFERROR(ABS(D61-validacion_snapshot!$U$108),1E+099)),IF(AND(E61="",validacion_snapshot!$V$108=""),0,IFERROR(ABS(E61-validacion_snapshot!$V$108),1E+099)),IF(AND(F61="",validacion_snapshot!$W$108=""),0,IFERROR(ABS(F61-validacion_snapshot!$W$108),1E+099)),IF(AND(H61="",validacion_snapshot!$Y$108=""),0,IFERROR(ABS(H61-validacion_snapshot!$Y$108),1E+099)),IF(AND(J61="",validacion_snapshot!$AA$108=""),0,IFERROR(ABS(J61-validacion_snapshot!$AA$108),1E+099)),IF(AND(L61="",validacion_snapshot!$AC$108=""),0,IFERROR(ABS(L61-validacion_snapshot!$AC$108),1E+099)))&lt;=0.00000001,G61=validacion_snapshot!$X$108,I61=validacion_snapshot!$Z$108,K61=validacion_snapshot!$AB$108,M61=validacion_snapshot!$AD$108),"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="N2:N61">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>N2="FALLA"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>N2="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="6.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$C:$C,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$D:$D,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$E:$E,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$F:$F,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$G:$G,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$H:$H,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$I:$I,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$J:$J,MATCH(D2,valor_asignado!$B:$B,0))</f>
+        <v>12</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(E2-validacion_snapshot!$K$109),ABS(F2-validacion_snapshot!$L$109),ABS(G2-validacion_snapshot!$M$109),ABS(H2-validacion_snapshot!$N$109),ABS(I2-validacion_snapshot!$O$109),ABS(J2-validacion_snapshot!$P$109),ABS(K2-validacion_snapshot!$Q$109),ABS(L2-validacion_snapshot!$R$109))&lt;=0.00000001,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$C:$C,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$D:$D,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$E:$E,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$F:$F,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$G:$G,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$H:$H,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$I:$I,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$J:$J,MATCH(D3,valor_asignado!$B:$B,0))</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(E3-validacion_snapshot!$K$110),ABS(F3-validacion_snapshot!$L$110),ABS(G3-validacion_snapshot!$M$110),ABS(H3-validacion_snapshot!$N$110),ABS(I3-validacion_snapshot!$O$110),ABS(J3-validacion_snapshot!$P$110),ABS(K3-validacion_snapshot!$Q$110),ABS(L3-validacion_snapshot!$R$110))&lt;=0.00000001,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$C:$C,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$D:$D,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$E:$E,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$F:$F,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$G:$G,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$H:$H,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$I:$I,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$J:$J,MATCH(D4,valor_asignado!$B:$B,0))</f>
+        <v>12</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(E4-validacion_snapshot!$K$111),ABS(F4-validacion_snapshot!$L$111),ABS(G4-validacion_snapshot!$M$111),ABS(H4-validacion_snapshot!$N$111),ABS(I4-validacion_snapshot!$O$111),ABS(J4-validacion_snapshot!$P$111),ABS(K4-validacion_snapshot!$Q$111),ABS(L4-validacion_snapshot!$R$111))&lt;=0.00000001,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$C:$C,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$D:$D,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$E:$E,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$F:$F,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$G:$G,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$H:$H,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$I:$I,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$J:$J,MATCH(D5,valor_asignado!$B:$B,0))</f>
+        <v>12</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(E5-validacion_snapshot!$K$112),ABS(F5-validacion_snapshot!$L$112),ABS(G5-validacion_snapshot!$M$112),ABS(H5-validacion_snapshot!$N$112),ABS(I5-validacion_snapshot!$O$112),ABS(J5-validacion_snapshot!$P$112),ABS(K5-validacion_snapshot!$Q$112),ABS(L5-validacion_snapshot!$R$112))&lt;=0.00000001,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$C:$C,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$D:$D,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$E:$E,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$F:$F,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$G:$G,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$H:$H,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$I:$I,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <f aca="false">INDEX(valor_asignado!$J:$J,MATCH(D6,valor_asignado!$B:$B,0))</f>
+        <v>12</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(E6-validacion_snapshot!$K$113),ABS(F6-validacion_snapshot!$L$113),ABS(G6-validacion_snapshot!$M$113),ABS(H6-validacion_snapshot!$N$113),ABS(I6-validacion_snapshot!$O$113),ABS(J6-validacion_snapshot!$P$113),ABS(K6-validacion_snapshot!$Q$113),ABS(L6-validacion_snapshot!$R$113))&lt;=0.00000001,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D7,puntajes_EA!$G:$G,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D7,puntajes_EA!$G:$G,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D7,puntajes_EA!$G:$G,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D7,puntajes_EA!$G:$G,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N7-validacion_snapshot!$AF$114),ABS(O7-validacion_snapshot!$AG$114),ABS(P7-validacion_snapshot!$AH$114),ABS(Q7-validacion_snapshot!$AI$114))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D8,puntajes_EA!$G:$G,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D8,puntajes_EA!$G:$G,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D8,puntajes_EA!$G:$G,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D8,puntajes_EA!$G:$G,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N8-validacion_snapshot!$AF$115),ABS(O8-validacion_snapshot!$AG$115),ABS(P8-validacion_snapshot!$AH$115),ABS(Q8-validacion_snapshot!$AI$115))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D9,puntajes_EA!$G:$G,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D9,puntajes_EA!$G:$G,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D9,puntajes_EA!$G:$G,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D9,puntajes_EA!$G:$G,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N9-validacion_snapshot!$AF$116),ABS(O9-validacion_snapshot!$AG$116),ABS(P9-validacion_snapshot!$AH$116),ABS(Q9-validacion_snapshot!$AI$116))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D10,puntajes_EA!$G:$G,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D10,puntajes_EA!$G:$G,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D10,puntajes_EA!$G:$G,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D10,puntajes_EA!$G:$G,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N10-validacion_snapshot!$AF$117),ABS(O10-validacion_snapshot!$AG$117),ABS(P10-validacion_snapshot!$AH$117),ABS(Q10-validacion_snapshot!$AI$117))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D11,puntajes_EA!$G:$G,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D11,puntajes_EA!$G:$G,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D11,puntajes_EA!$G:$G,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D11,puntajes_EA!$G:$G,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N11-validacion_snapshot!$AF$118),ABS(O11-validacion_snapshot!$AG$118),ABS(P11-validacion_snapshot!$AH$118),ABS(Q11-validacion_snapshot!$AI$118))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D12,puntajes_EA!$I:$I,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D12,puntajes_EA!$I:$I,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D12,puntajes_EA!$I:$I,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D12,puntajes_EA!$I:$I,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N12-validacion_snapshot!$AF$119),ABS(O12-validacion_snapshot!$AG$119),ABS(P12-validacion_snapshot!$AH$119),ABS(Q12-validacion_snapshot!$AI$119))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D13,puntajes_EA!$I:$I,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D13,puntajes_EA!$I:$I,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D13,puntajes_EA!$I:$I,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D13,puntajes_EA!$I:$I,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N13-validacion_snapshot!$AF$120),ABS(O13-validacion_snapshot!$AG$120),ABS(P13-validacion_snapshot!$AH$120),ABS(Q13-validacion_snapshot!$AI$120))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D14,puntajes_EA!$I:$I,"N/A")</f>
+        <v>12</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D14,puntajes_EA!$I:$I,"Satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D14,puntajes_EA!$I:$I,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D14,puntajes_EA!$I:$I,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N14-validacion_snapshot!$AF$121),ABS(O14-validacion_snapshot!$AG$121),ABS(P14-validacion_snapshot!$AH$121),ABS(Q14-validacion_snapshot!$AI$121))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D15,puntajes_EA!$I:$I,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D15,puntajes_EA!$I:$I,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D15,puntajes_EA!$I:$I,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D15,puntajes_EA!$I:$I,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N15-validacion_snapshot!$AF$122),ABS(O15-validacion_snapshot!$AG$122),ABS(P15-validacion_snapshot!$AH$122),ABS(Q15-validacion_snapshot!$AI$122))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D16,puntajes_EA!$I:$I,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D16,puntajes_EA!$I:$I,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D16,puntajes_EA!$I:$I,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D16,puntajes_EA!$I:$I,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N16-validacion_snapshot!$AF$123),ABS(O16-validacion_snapshot!$AG$123),ABS(P16-validacion_snapshot!$AH$123),ABS(Q16-validacion_snapshot!$AI$123))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D17,puntajes_EA!$K:$K,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D17,puntajes_EA!$K:$K,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D17,puntajes_EA!$K:$K,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D17,puntajes_EA!$K:$K,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N17-validacion_snapshot!$AF$124),ABS(O17-validacion_snapshot!$AG$124),ABS(P17-validacion_snapshot!$AH$124),ABS(Q17-validacion_snapshot!$AI$124))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D18,puntajes_EA!$K:$K,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D18,puntajes_EA!$K:$K,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D18,puntajes_EA!$K:$K,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D18,puntajes_EA!$K:$K,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N18-validacion_snapshot!$AF$125),ABS(O18-validacion_snapshot!$AG$125),ABS(P18-validacion_snapshot!$AH$125),ABS(Q18-validacion_snapshot!$AI$125))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D19,puntajes_EA!$K:$K,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D19,puntajes_EA!$K:$K,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D19,puntajes_EA!$K:$K,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D19,puntajes_EA!$K:$K,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N19-validacion_snapshot!$AF$126),ABS(O19-validacion_snapshot!$AG$126),ABS(P19-validacion_snapshot!$AH$126),ABS(Q19-validacion_snapshot!$AI$126))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D20,puntajes_EA!$K:$K,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D20,puntajes_EA!$K:$K,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D20,puntajes_EA!$K:$K,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D20,puntajes_EA!$K:$K,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N20-validacion_snapshot!$AF$127),ABS(O20-validacion_snapshot!$AG$127),ABS(P20-validacion_snapshot!$AH$127),ABS(Q20-validacion_snapshot!$AI$127))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D21,puntajes_EA!$K:$K,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D21,puntajes_EA!$K:$K,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D21,puntajes_EA!$K:$K,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D21,puntajes_EA!$K:$K,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N21-validacion_snapshot!$AF$128),ABS(O21-validacion_snapshot!$AG$128),ABS(P21-validacion_snapshot!$AH$128),ABS(Q21-validacion_snapshot!$AI$128))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D22,puntajes_EA!$M:$M,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D22,puntajes_EA!$M:$M,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D22,puntajes_EA!$M:$M,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D22,puntajes_EA!$M:$M,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N22-validacion_snapshot!$AF$129),ABS(O22-validacion_snapshot!$AG$129),ABS(P22-validacion_snapshot!$AH$129),ABS(Q22-validacion_snapshot!$AI$129))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D23,puntajes_EA!$M:$M,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D23,puntajes_EA!$M:$M,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D23,puntajes_EA!$M:$M,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D23,puntajes_EA!$M:$M,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N23-validacion_snapshot!$AF$130),ABS(O23-validacion_snapshot!$AG$130),ABS(P23-validacion_snapshot!$AH$130),ABS(Q23-validacion_snapshot!$AI$130))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D24,puntajes_EA!$M:$M,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D24,puntajes_EA!$M:$M,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D24,puntajes_EA!$M:$M,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D24,puntajes_EA!$M:$M,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N24-validacion_snapshot!$AF$131),ABS(O24-validacion_snapshot!$AG$131),ABS(P24-validacion_snapshot!$AH$131),ABS(Q24-validacion_snapshot!$AI$131))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D25,puntajes_EA!$M:$M,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D25,puntajes_EA!$M:$M,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D25,puntajes_EA!$M:$M,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D25,puntajes_EA!$M:$M,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N25-validacion_snapshot!$AF$132),ABS(O25-validacion_snapshot!$AG$132),ABS(P25-validacion_snapshot!$AH$132),ABS(Q25-validacion_snapshot!$AI$132))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D26,puntajes_EA!$M:$M,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D26,puntajes_EA!$M:$M,"Satisfactorio")</f>
+        <v>12</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D26,puntajes_EA!$M:$M,"Cuestionable")</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <f aca="false">COUNTIFS(puntajes_EA!$B:$B,D26,puntajes_EA!$M:$M,"No satisfactorio")</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="str">
+        <f aca="false">IF(SUM(ABS(N26-validacion_snapshot!$AF$133),ABS(O26-validacion_snapshot!$AG$133),ABS(P26-validacion_snapshot!$AH$133),ABS(Q26-validacion_snapshot!$AI$133))=0,"OK","FALLA")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="R2:R26">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>R2="FALLA"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>R2="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:AI133"/>
   <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8401,19 +12946,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>64</v>
@@ -8461,49 +13006,49 @@
         <v>112</v>
       </c>
       <c r="U1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8520,7 +13065,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>70</v>
@@ -8573,7 +13118,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>70</v>
@@ -8626,7 +13171,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>70</v>
@@ -8679,7 +13224,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>70</v>
@@ -8732,7 +13277,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>70</v>
@@ -8785,7 +13330,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>70</v>
@@ -8838,7 +13383,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>79</v>
@@ -8891,7 +13436,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>79</v>
@@ -8944,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>79</v>
@@ -8997,7 +13542,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>79</v>
@@ -9050,7 +13595,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>79</v>
@@ -9103,7 +13648,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>79</v>
@@ -9156,7 +13701,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>79</v>
@@ -9209,7 +13754,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>79</v>
@@ -9262,7 +13807,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>70</v>
@@ -9315,7 +13860,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>70</v>
@@ -9368,7 +13913,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>70</v>
@@ -9421,7 +13966,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>70</v>
@@ -9474,7 +14019,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>70</v>
@@ -9527,7 +14072,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>70</v>
@@ -9580,7 +14125,7 @@
         <v>6</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>79</v>
@@ -9633,7 +14178,7 @@
         <v>6</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>79</v>
@@ -9686,7 +14231,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>79</v>
@@ -9739,7 +14284,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>79</v>
@@ -9792,7 +14337,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>79</v>
@@ -9845,7 +14390,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>79</v>
@@ -9898,7 +14443,7 @@
         <v>6</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>79</v>
@@ -9951,7 +14496,7 @@
         <v>6</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>79</v>
@@ -10004,7 +14549,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
@@ -10019,7 +14564,7 @@
         <v>192</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M30" s="8" t="s">
         <v>192</v>
@@ -10037,7 +14582,7 @@
         <v>192</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
@@ -10071,7 +14616,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
@@ -10104,7 +14649,7 @@
         <v>192</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
@@ -10138,7 +14683,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -10171,7 +14716,7 @@
         <v>192</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S32" s="8"/>
       <c r="T32" s="8"/>
@@ -10205,7 +14750,7 @@
         <v>6</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -10238,7 +14783,7 @@
         <v>192</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
@@ -10272,7 +14817,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
@@ -10287,7 +14832,7 @@
         <v>192</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>192</v>
@@ -10305,7 +14850,7 @@
         <v>192</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
@@ -10339,7 +14884,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
@@ -10392,7 +14937,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="s">
@@ -10445,7 +14990,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="s">
@@ -10498,7 +15043,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="s">
@@ -10551,7 +15096,7 @@
         <v>6</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8" t="s">
@@ -10604,7 +15149,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8" t="s">
@@ -10657,7 +15202,7 @@
         <v>6</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
@@ -10710,7 +15255,7 @@
         <v>6</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="s">
@@ -10763,7 +15308,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="s">
@@ -10816,7 +15361,7 @@
         <v>6</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
@@ -10869,7 +15414,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8" t="s">
@@ -10922,7 +15467,7 @@
         <v>6</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
@@ -10975,7 +15520,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
@@ -11028,7 +15573,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8" t="s">
@@ -11081,7 +15626,7 @@
         <v>6</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -11106,31 +15651,31 @@
         <v>192</v>
       </c>
       <c r="V49" s="8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="W49" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X49" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y49" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z49" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA49" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB49" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC49" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD49" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE49" s="8"/>
       <c r="AF49" s="8"/>
@@ -11152,7 +15697,7 @@
         <v>6</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -11177,31 +15722,31 @@
         <v>192</v>
       </c>
       <c r="V50" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W50" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X50" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y50" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z50" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA50" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB50" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC50" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD50" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE50" s="8"/>
       <c r="AF50" s="8"/>
@@ -11223,7 +15768,7 @@
         <v>6</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -11248,31 +15793,31 @@
         <v>192</v>
       </c>
       <c r="V51" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W51" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X51" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y51" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z51" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA51" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB51" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC51" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD51" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE51" s="8"/>
       <c r="AF51" s="8"/>
@@ -11294,7 +15839,7 @@
         <v>6</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
@@ -11319,31 +15864,31 @@
         <v>192</v>
       </c>
       <c r="V52" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W52" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X52" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y52" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z52" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA52" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB52" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC52" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD52" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
@@ -11365,7 +15910,7 @@
         <v>6</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
@@ -11390,31 +15935,31 @@
         <v>192</v>
       </c>
       <c r="V53" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W53" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X53" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y53" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z53" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA53" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB53" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC53" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD53" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE53" s="8"/>
       <c r="AF53" s="8"/>
@@ -11436,7 +15981,7 @@
         <v>6</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
@@ -11461,31 +16006,31 @@
         <v>192</v>
       </c>
       <c r="V54" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W54" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X54" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y54" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z54" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA54" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB54" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC54" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD54" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
@@ -11507,7 +16052,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
@@ -11532,31 +16077,31 @@
         <v>192</v>
       </c>
       <c r="V55" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W55" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X55" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y55" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z55" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA55" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB55" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC55" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD55" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE55" s="8"/>
       <c r="AF55" s="8"/>
@@ -11578,7 +16123,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -11603,31 +16148,31 @@
         <v>192</v>
       </c>
       <c r="V56" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W56" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X56" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y56" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z56" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA56" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB56" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC56" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD56" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
@@ -11649,7 +16194,7 @@
         <v>6</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
@@ -11674,31 +16219,31 @@
         <v>192</v>
       </c>
       <c r="V57" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W57" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X57" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y57" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z57" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA57" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB57" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC57" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD57" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
@@ -11720,7 +16265,7 @@
         <v>6</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
@@ -11745,31 +16290,31 @@
         <v>192</v>
       </c>
       <c r="V58" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W58" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X58" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y58" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z58" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA58" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB58" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC58" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD58" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE58" s="8"/>
       <c r="AF58" s="8"/>
@@ -11791,7 +16336,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
@@ -11816,31 +16361,31 @@
         <v>192</v>
       </c>
       <c r="V59" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W59" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X59" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y59" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z59" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA59" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB59" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC59" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD59" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE59" s="8"/>
       <c r="AF59" s="8"/>
@@ -11862,7 +16407,7 @@
         <v>6</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
@@ -11887,31 +16432,31 @@
         <v>192</v>
       </c>
       <c r="V60" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W60" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X60" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y60" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z60" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA60" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB60" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC60" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD60" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE60" s="8"/>
       <c r="AF60" s="8"/>
@@ -11933,7 +16478,7 @@
         <v>6</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
@@ -11958,27 +16503,27 @@
         <v>192</v>
       </c>
       <c r="V61" s="8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="W61" s="8"/>
       <c r="X61" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y61" s="8"/>
       <c r="Z61" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA61" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB61" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC61" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD61" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE61" s="8"/>
       <c r="AF61" s="8"/>
@@ -12000,7 +16545,7 @@
         <v>6</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
@@ -12025,27 +16570,27 @@
         <v>192</v>
       </c>
       <c r="V62" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W62" s="8"/>
       <c r="X62" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y62" s="8"/>
       <c r="Z62" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA62" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB62" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC62" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD62" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE62" s="8"/>
       <c r="AF62" s="8"/>
@@ -12067,7 +16612,7 @@
         <v>6</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
@@ -12092,27 +16637,27 @@
         <v>192</v>
       </c>
       <c r="V63" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W63" s="8"/>
       <c r="X63" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y63" s="8"/>
       <c r="Z63" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA63" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB63" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC63" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD63" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE63" s="8"/>
       <c r="AF63" s="8"/>
@@ -12134,7 +16679,7 @@
         <v>6</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
@@ -12159,27 +16704,27 @@
         <v>192</v>
       </c>
       <c r="V64" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W64" s="8"/>
       <c r="X64" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y64" s="8"/>
       <c r="Z64" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA64" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB64" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC64" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD64" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE64" s="8"/>
       <c r="AF64" s="8"/>
@@ -12201,7 +16746,7 @@
         <v>6</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -12226,27 +16771,27 @@
         <v>192</v>
       </c>
       <c r="V65" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA65" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB65" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC65" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD65" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE65" s="8"/>
       <c r="AF65" s="8"/>
@@ -12268,7 +16813,7 @@
         <v>6</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
@@ -12293,27 +16838,27 @@
         <v>192</v>
       </c>
       <c r="V66" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W66" s="8"/>
       <c r="X66" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y66" s="8"/>
       <c r="Z66" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA66" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB66" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC66" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD66" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE66" s="8"/>
       <c r="AF66" s="8"/>
@@ -12335,7 +16880,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
@@ -12360,27 +16905,27 @@
         <v>192</v>
       </c>
       <c r="V67" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W67" s="8"/>
       <c r="X67" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y67" s="8"/>
       <c r="Z67" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA67" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB67" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC67" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD67" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE67" s="8"/>
       <c r="AF67" s="8"/>
@@ -12402,7 +16947,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
@@ -12427,27 +16972,27 @@
         <v>192</v>
       </c>
       <c r="V68" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W68" s="8"/>
       <c r="X68" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y68" s="8"/>
       <c r="Z68" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA68" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB68" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC68" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD68" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE68" s="8"/>
       <c r="AF68" s="8"/>
@@ -12469,7 +17014,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
@@ -12494,27 +17039,27 @@
         <v>192</v>
       </c>
       <c r="V69" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W69" s="8"/>
       <c r="X69" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y69" s="8"/>
       <c r="Z69" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA69" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB69" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC69" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD69" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE69" s="8"/>
       <c r="AF69" s="8"/>
@@ -12536,7 +17081,7 @@
         <v>6</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
@@ -12561,27 +17106,27 @@
         <v>192</v>
       </c>
       <c r="V70" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W70" s="8"/>
       <c r="X70" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y70" s="8"/>
       <c r="Z70" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA70" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB70" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC70" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD70" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE70" s="8"/>
       <c r="AF70" s="8"/>
@@ -12603,7 +17148,7 @@
         <v>6</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
@@ -12628,27 +17173,27 @@
         <v>192</v>
       </c>
       <c r="V71" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W71" s="8"/>
       <c r="X71" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y71" s="8"/>
       <c r="Z71" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA71" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB71" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC71" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD71" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE71" s="8"/>
       <c r="AF71" s="8"/>
@@ -12670,7 +17215,7 @@
         <v>6</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -12695,27 +17240,27 @@
         <v>192</v>
       </c>
       <c r="V72" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W72" s="8"/>
       <c r="X72" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y72" s="8"/>
       <c r="Z72" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA72" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB72" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC72" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD72" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE72" s="8"/>
       <c r="AF72" s="8"/>
@@ -12737,7 +17282,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
@@ -12762,27 +17307,27 @@
         <v>192</v>
       </c>
       <c r="V73" s="8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="W73" s="8"/>
       <c r="X73" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y73" s="8"/>
       <c r="Z73" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA73" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB73" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC73" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD73" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE73" s="8"/>
       <c r="AF73" s="8"/>
@@ -12804,7 +17349,7 @@
         <v>6</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
@@ -12829,27 +17374,27 @@
         <v>192</v>
       </c>
       <c r="V74" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W74" s="8"/>
       <c r="X74" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y74" s="8"/>
       <c r="Z74" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA74" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB74" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC74" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD74" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE74" s="8"/>
       <c r="AF74" s="8"/>
@@ -12871,7 +17416,7 @@
         <v>6</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
@@ -12896,27 +17441,27 @@
         <v>192</v>
       </c>
       <c r="V75" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W75" s="8"/>
       <c r="X75" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y75" s="8"/>
       <c r="Z75" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA75" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB75" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC75" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD75" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE75" s="8"/>
       <c r="AF75" s="8"/>
@@ -12938,7 +17483,7 @@
         <v>6</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
@@ -12963,27 +17508,27 @@
         <v>192</v>
       </c>
       <c r="V76" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W76" s="8"/>
       <c r="X76" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y76" s="8"/>
       <c r="Z76" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA76" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB76" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC76" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD76" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE76" s="8"/>
       <c r="AF76" s="8"/>
@@ -13005,7 +17550,7 @@
         <v>6</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
@@ -13030,27 +17575,27 @@
         <v>192</v>
       </c>
       <c r="V77" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W77" s="8"/>
       <c r="X77" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y77" s="8"/>
       <c r="Z77" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA77" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB77" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC77" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD77" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE77" s="8"/>
       <c r="AF77" s="8"/>
@@ -13072,7 +17617,7 @@
         <v>6</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
@@ -13097,27 +17642,27 @@
         <v>192</v>
       </c>
       <c r="V78" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W78" s="8"/>
       <c r="X78" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y78" s="8"/>
       <c r="Z78" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA78" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB78" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC78" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD78" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE78" s="8"/>
       <c r="AF78" s="8"/>
@@ -13139,7 +17684,7 @@
         <v>6</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
@@ -13164,27 +17709,27 @@
         <v>192</v>
       </c>
       <c r="V79" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W79" s="8"/>
       <c r="X79" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y79" s="8"/>
       <c r="Z79" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA79" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB79" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC79" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD79" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE79" s="8"/>
       <c r="AF79" s="8"/>
@@ -13206,7 +17751,7 @@
         <v>6</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
@@ -13231,27 +17776,27 @@
         <v>192</v>
       </c>
       <c r="V80" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W80" s="8"/>
       <c r="X80" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y80" s="8"/>
       <c r="Z80" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA80" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB80" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC80" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD80" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE80" s="8"/>
       <c r="AF80" s="8"/>
@@ -13273,7 +17818,7 @@
         <v>6</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
@@ -13298,27 +17843,27 @@
         <v>192</v>
       </c>
       <c r="V81" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W81" s="8"/>
       <c r="X81" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y81" s="8"/>
       <c r="Z81" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA81" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB81" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC81" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD81" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE81" s="8"/>
       <c r="AF81" s="8"/>
@@ -13340,7 +17885,7 @@
         <v>6</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
@@ -13365,27 +17910,27 @@
         <v>192</v>
       </c>
       <c r="V82" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W82" s="8"/>
       <c r="X82" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y82" s="8"/>
       <c r="Z82" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA82" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB82" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC82" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD82" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE82" s="8"/>
       <c r="AF82" s="8"/>
@@ -13407,7 +17952,7 @@
         <v>6</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
@@ -13432,27 +17977,27 @@
         <v>192</v>
       </c>
       <c r="V83" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W83" s="8"/>
       <c r="X83" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y83" s="8"/>
       <c r="Z83" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA83" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB83" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC83" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD83" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE83" s="8"/>
       <c r="AF83" s="8"/>
@@ -13474,7 +18019,7 @@
         <v>6</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
@@ -13499,27 +18044,27 @@
         <v>192</v>
       </c>
       <c r="V84" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W84" s="8"/>
       <c r="X84" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y84" s="8"/>
       <c r="Z84" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA84" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB84" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC84" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD84" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE84" s="8"/>
       <c r="AF84" s="8"/>
@@ -13541,7 +18086,7 @@
         <v>6</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
@@ -13566,27 +18111,27 @@
         <v>192</v>
       </c>
       <c r="V85" s="8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="W85" s="8"/>
       <c r="X85" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y85" s="8"/>
       <c r="Z85" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA85" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB85" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC85" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD85" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE85" s="8"/>
       <c r="AF85" s="8"/>
@@ -13608,7 +18153,7 @@
         <v>6</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
@@ -13633,27 +18178,27 @@
         <v>192</v>
       </c>
       <c r="V86" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W86" s="8"/>
       <c r="X86" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y86" s="8"/>
       <c r="Z86" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA86" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB86" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC86" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD86" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE86" s="8"/>
       <c r="AF86" s="8"/>
@@ -13675,7 +18220,7 @@
         <v>6</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
@@ -13700,27 +18245,27 @@
         <v>192</v>
       </c>
       <c r="V87" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W87" s="8"/>
       <c r="X87" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y87" s="8"/>
       <c r="Z87" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA87" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB87" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC87" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD87" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE87" s="8"/>
       <c r="AF87" s="8"/>
@@ -13742,7 +18287,7 @@
         <v>6</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
@@ -13767,27 +18312,27 @@
         <v>192</v>
       </c>
       <c r="V88" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W88" s="8"/>
       <c r="X88" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y88" s="8"/>
       <c r="Z88" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA88" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB88" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC88" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD88" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE88" s="8"/>
       <c r="AF88" s="8"/>
@@ -13809,7 +18354,7 @@
         <v>6</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
@@ -13834,27 +18379,27 @@
         <v>192</v>
       </c>
       <c r="V89" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W89" s="8"/>
       <c r="X89" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y89" s="8"/>
       <c r="Z89" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA89" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB89" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC89" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD89" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE89" s="8"/>
       <c r="AF89" s="8"/>
@@ -13876,7 +18421,7 @@
         <v>6</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
@@ -13901,27 +18446,27 @@
         <v>192</v>
       </c>
       <c r="V90" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W90" s="8"/>
       <c r="X90" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y90" s="8"/>
       <c r="Z90" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA90" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB90" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC90" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD90" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE90" s="8"/>
       <c r="AF90" s="8"/>
@@ -13943,7 +18488,7 @@
         <v>6</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
@@ -13968,27 +18513,27 @@
         <v>192</v>
       </c>
       <c r="V91" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W91" s="8"/>
       <c r="X91" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y91" s="8"/>
       <c r="Z91" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA91" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB91" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC91" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD91" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE91" s="8"/>
       <c r="AF91" s="8"/>
@@ -14010,7 +18555,7 @@
         <v>6</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
@@ -14035,27 +18580,27 @@
         <v>192</v>
       </c>
       <c r="V92" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W92" s="8"/>
       <c r="X92" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y92" s="8"/>
       <c r="Z92" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA92" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB92" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC92" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD92" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE92" s="8"/>
       <c r="AF92" s="8"/>
@@ -14077,7 +18622,7 @@
         <v>6</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
@@ -14102,27 +18647,27 @@
         <v>192</v>
       </c>
       <c r="V93" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W93" s="8"/>
       <c r="X93" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y93" s="8"/>
       <c r="Z93" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA93" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB93" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC93" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD93" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE93" s="8"/>
       <c r="AF93" s="8"/>
@@ -14144,7 +18689,7 @@
         <v>6</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
@@ -14169,27 +18714,27 @@
         <v>192</v>
       </c>
       <c r="V94" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W94" s="8"/>
       <c r="X94" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y94" s="8"/>
       <c r="Z94" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA94" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB94" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC94" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD94" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE94" s="8"/>
       <c r="AF94" s="8"/>
@@ -14211,7 +18756,7 @@
         <v>6</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
@@ -14236,27 +18781,27 @@
         <v>192</v>
       </c>
       <c r="V95" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W95" s="8"/>
       <c r="X95" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y95" s="8"/>
       <c r="Z95" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA95" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB95" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC95" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD95" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE95" s="8"/>
       <c r="AF95" s="8"/>
@@ -14278,7 +18823,7 @@
         <v>6</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
@@ -14303,27 +18848,27 @@
         <v>192</v>
       </c>
       <c r="V96" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W96" s="8"/>
       <c r="X96" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Y96" s="8"/>
       <c r="Z96" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA96" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB96" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC96" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD96" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE96" s="8"/>
       <c r="AF96" s="8"/>
@@ -14345,7 +18890,7 @@
         <v>6</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
@@ -14370,31 +18915,31 @@
         <v>192</v>
       </c>
       <c r="V97" s="8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="W97" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X97" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y97" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z97" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA97" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB97" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC97" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD97" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE97" s="8"/>
       <c r="AF97" s="8"/>
@@ -14416,7 +18961,7 @@
         <v>6</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
@@ -14441,31 +18986,31 @@
         <v>192</v>
       </c>
       <c r="V98" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W98" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X98" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y98" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z98" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA98" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB98" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC98" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD98" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE98" s="8"/>
       <c r="AF98" s="8"/>
@@ -14487,7 +19032,7 @@
         <v>6</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
@@ -14512,31 +19057,31 @@
         <v>192</v>
       </c>
       <c r="V99" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W99" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X99" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y99" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z99" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA99" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB99" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC99" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD99" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE99" s="8"/>
       <c r="AF99" s="8"/>
@@ -14558,7 +19103,7 @@
         <v>6</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
@@ -14583,31 +19128,31 @@
         <v>192</v>
       </c>
       <c r="V100" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W100" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X100" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y100" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z100" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA100" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB100" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC100" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD100" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE100" s="8"/>
       <c r="AF100" s="8"/>
@@ -14629,7 +19174,7 @@
         <v>6</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
@@ -14654,31 +19199,31 @@
         <v>192</v>
       </c>
       <c r="V101" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W101" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X101" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y101" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z101" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA101" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB101" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC101" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD101" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE101" s="8"/>
       <c r="AF101" s="8"/>
@@ -14700,7 +19245,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
@@ -14725,31 +19270,31 @@
         <v>192</v>
       </c>
       <c r="V102" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W102" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X102" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y102" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z102" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA102" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB102" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC102" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD102" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE102" s="8"/>
       <c r="AF102" s="8"/>
@@ -14771,7 +19316,7 @@
         <v>6</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
@@ -14796,31 +19341,31 @@
         <v>192</v>
       </c>
       <c r="V103" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W103" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X103" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y103" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z103" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA103" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB103" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC103" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD103" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE103" s="8"/>
       <c r="AF103" s="8"/>
@@ -14842,7 +19387,7 @@
         <v>6</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
@@ -14867,31 +19412,31 @@
         <v>192</v>
       </c>
       <c r="V104" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W104" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X104" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y104" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z104" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA104" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB104" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC104" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD104" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE104" s="8"/>
       <c r="AF104" s="8"/>
@@ -14913,7 +19458,7 @@
         <v>6</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
@@ -14938,31 +19483,31 @@
         <v>192</v>
       </c>
       <c r="V105" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W105" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X105" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y105" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z105" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA105" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB105" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC105" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD105" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE105" s="8"/>
       <c r="AF105" s="8"/>
@@ -14984,7 +19529,7 @@
         <v>6</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
@@ -15009,31 +19554,31 @@
         <v>192</v>
       </c>
       <c r="V106" s="8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W106" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X106" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y106" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z106" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA106" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB106" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC106" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD106" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE106" s="8"/>
       <c r="AF106" s="8"/>
@@ -15055,7 +19600,7 @@
         <v>6</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
@@ -15080,31 +19625,31 @@
         <v>192</v>
       </c>
       <c r="V107" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W107" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X107" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y107" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z107" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA107" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB107" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC107" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD107" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE107" s="8"/>
       <c r="AF107" s="8"/>
@@ -15126,7 +19671,7 @@
         <v>6</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
@@ -15151,31 +19696,31 @@
         <v>192</v>
       </c>
       <c r="V108" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W108" s="8" t="s">
         <v>192</v>
       </c>
       <c r="X108" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y108" s="8" t="s">
         <v>192</v>
       </c>
       <c r="Z108" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA108" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AB108" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AC108" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AD108" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AE108" s="8"/>
       <c r="AF108" s="8"/>
@@ -15197,10 +19742,10 @@
         <v>6</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
@@ -15214,7 +19759,7 @@
         <v>192</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M109" s="8" t="s">
         <v>192</v>
@@ -15232,10 +19777,10 @@
         <v>192</v>
       </c>
       <c r="R109" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S109" s="8" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="T109" s="8"/>
       <c r="U109" s="8"/>
@@ -15268,10 +19813,10 @@
         <v>6</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
@@ -15303,10 +19848,10 @@
         <v>192</v>
       </c>
       <c r="R110" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="T110" s="8"/>
       <c r="U110" s="8"/>
@@ -15339,10 +19884,10 @@
         <v>6</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
@@ -15374,10 +19919,10 @@
         <v>192</v>
       </c>
       <c r="R111" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S111" s="8" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="T111" s="8"/>
       <c r="U111" s="8"/>
@@ -15410,10 +19955,10 @@
         <v>6</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
@@ -15445,10 +19990,10 @@
         <v>192</v>
       </c>
       <c r="R112" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S112" s="8" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="T112" s="8"/>
       <c r="U112" s="8"/>
@@ -15481,10 +20026,10 @@
         <v>6</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
@@ -15498,7 +20043,7 @@
         <v>192</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M113" s="8" t="s">
         <v>192</v>
@@ -15516,10 +20061,10 @@
         <v>192</v>
       </c>
       <c r="R113" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S113" s="8" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="T113" s="8"/>
       <c r="U113" s="8"/>
@@ -15552,10 +20097,10 @@
         <v>6</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
@@ -15572,7 +20117,7 @@
       <c r="Q114" s="8"/>
       <c r="R114" s="8"/>
       <c r="S114" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T114" s="8"/>
       <c r="U114" s="8"/>
@@ -15586,10 +20131,10 @@
       <c r="AC114" s="8"/>
       <c r="AD114" s="8"/>
       <c r="AE114" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AF114" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG114" s="8" t="s">
         <v>192</v>
@@ -15615,10 +20160,10 @@
         <v>6</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
@@ -15635,7 +20180,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="8"/>
       <c r="S115" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T115" s="8"/>
       <c r="U115" s="8"/>
@@ -15649,10 +20194,10 @@
       <c r="AC115" s="8"/>
       <c r="AD115" s="8"/>
       <c r="AE115" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AF115" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG115" s="8" t="s">
         <v>192</v>
@@ -15678,10 +20223,10 @@
         <v>6</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
@@ -15698,7 +20243,7 @@
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
       <c r="S116" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T116" s="8"/>
       <c r="U116" s="8"/>
@@ -15712,10 +20257,10 @@
       <c r="AC116" s="8"/>
       <c r="AD116" s="8"/>
       <c r="AE116" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AF116" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG116" s="8" t="s">
         <v>192</v>
@@ -15741,10 +20286,10 @@
         <v>6</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
@@ -15761,7 +20306,7 @@
       <c r="Q117" s="8"/>
       <c r="R117" s="8"/>
       <c r="S117" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T117" s="8"/>
       <c r="U117" s="8"/>
@@ -15775,13 +20320,13 @@
       <c r="AC117" s="8"/>
       <c r="AD117" s="8"/>
       <c r="AE117" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AF117" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG117" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH117" s="8" t="s">
         <v>192</v>
@@ -15804,10 +20349,10 @@
         <v>6</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
@@ -15824,7 +20369,7 @@
       <c r="Q118" s="8"/>
       <c r="R118" s="8"/>
       <c r="S118" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T118" s="8"/>
       <c r="U118" s="8"/>
@@ -15838,13 +20383,13 @@
       <c r="AC118" s="8"/>
       <c r="AD118" s="8"/>
       <c r="AE118" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AF118" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG118" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH118" s="8" t="s">
         <v>192</v>
@@ -15867,10 +20412,10 @@
         <v>6</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
@@ -15887,7 +20432,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="8"/>
       <c r="S119" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T119" s="8"/>
       <c r="U119" s="8"/>
@@ -15901,10 +20446,10 @@
       <c r="AC119" s="8"/>
       <c r="AD119" s="8"/>
       <c r="AE119" s="8" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="AF119" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG119" s="8" t="s">
         <v>192</v>
@@ -15930,10 +20475,10 @@
         <v>6</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
@@ -15950,7 +20495,7 @@
       <c r="Q120" s="8"/>
       <c r="R120" s="8"/>
       <c r="S120" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T120" s="8"/>
       <c r="U120" s="8"/>
@@ -15964,10 +20509,10 @@
       <c r="AC120" s="8"/>
       <c r="AD120" s="8"/>
       <c r="AE120" s="8" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="AF120" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG120" s="8" t="s">
         <v>192</v>
@@ -15993,10 +20538,10 @@
         <v>6</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
@@ -16013,7 +20558,7 @@
       <c r="Q121" s="8"/>
       <c r="R121" s="8"/>
       <c r="S121" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T121" s="8"/>
       <c r="U121" s="8"/>
@@ -16027,10 +20572,10 @@
       <c r="AC121" s="8"/>
       <c r="AD121" s="8"/>
       <c r="AE121" s="8" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="AF121" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG121" s="8" t="s">
         <v>192</v>
@@ -16056,10 +20601,10 @@
         <v>6</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
@@ -16076,7 +20621,7 @@
       <c r="Q122" s="8"/>
       <c r="R122" s="8"/>
       <c r="S122" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T122" s="8"/>
       <c r="U122" s="8"/>
@@ -16090,13 +20635,13 @@
       <c r="AC122" s="8"/>
       <c r="AD122" s="8"/>
       <c r="AE122" s="8" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="AF122" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG122" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH122" s="8" t="s">
         <v>192</v>
@@ -16119,10 +20664,10 @@
         <v>6</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
@@ -16139,7 +20684,7 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="8"/>
       <c r="S123" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T123" s="8"/>
       <c r="U123" s="8"/>
@@ -16153,13 +20698,13 @@
       <c r="AC123" s="8"/>
       <c r="AD123" s="8"/>
       <c r="AE123" s="8" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="AF123" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG123" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH123" s="8" t="s">
         <v>192</v>
@@ -16182,10 +20727,10 @@
         <v>6</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
@@ -16202,7 +20747,7 @@
       <c r="Q124" s="8"/>
       <c r="R124" s="8"/>
       <c r="S124" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T124" s="8"/>
       <c r="U124" s="8"/>
@@ -16216,13 +20761,13 @@
       <c r="AC124" s="8"/>
       <c r="AD124" s="8"/>
       <c r="AE124" s="8" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="AF124" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG124" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH124" s="8" t="s">
         <v>192</v>
@@ -16245,10 +20790,10 @@
         <v>6</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
@@ -16265,7 +20810,7 @@
       <c r="Q125" s="8"/>
       <c r="R125" s="8"/>
       <c r="S125" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T125" s="8"/>
       <c r="U125" s="8"/>
@@ -16279,13 +20824,13 @@
       <c r="AC125" s="8"/>
       <c r="AD125" s="8"/>
       <c r="AE125" s="8" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="AF125" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG125" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH125" s="8" t="s">
         <v>192</v>
@@ -16308,10 +20853,10 @@
         <v>6</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
@@ -16328,7 +20873,7 @@
       <c r="Q126" s="8"/>
       <c r="R126" s="8"/>
       <c r="S126" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T126" s="8"/>
       <c r="U126" s="8"/>
@@ -16342,13 +20887,13 @@
       <c r="AC126" s="8"/>
       <c r="AD126" s="8"/>
       <c r="AE126" s="8" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="AF126" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG126" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH126" s="8" t="s">
         <v>192</v>
@@ -16371,10 +20916,10 @@
         <v>6</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
@@ -16391,7 +20936,7 @@
       <c r="Q127" s="8"/>
       <c r="R127" s="8"/>
       <c r="S127" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T127" s="8"/>
       <c r="U127" s="8"/>
@@ -16405,13 +20950,13 @@
       <c r="AC127" s="8"/>
       <c r="AD127" s="8"/>
       <c r="AE127" s="8" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="AF127" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG127" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH127" s="8" t="s">
         <v>192</v>
@@ -16434,10 +20979,10 @@
         <v>6</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
@@ -16454,7 +20999,7 @@
       <c r="Q128" s="8"/>
       <c r="R128" s="8"/>
       <c r="S128" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T128" s="8"/>
       <c r="U128" s="8"/>
@@ -16468,13 +21013,13 @@
       <c r="AC128" s="8"/>
       <c r="AD128" s="8"/>
       <c r="AE128" s="8" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="AF128" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG128" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH128" s="8" t="s">
         <v>192</v>
@@ -16497,10 +21042,10 @@
         <v>6</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
@@ -16517,7 +21062,7 @@
       <c r="Q129" s="8"/>
       <c r="R129" s="8"/>
       <c r="S129" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T129" s="8"/>
       <c r="U129" s="8"/>
@@ -16531,13 +21076,13 @@
       <c r="AC129" s="8"/>
       <c r="AD129" s="8"/>
       <c r="AE129" s="8" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AF129" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG129" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH129" s="8" t="s">
         <v>192</v>
@@ -16560,10 +21105,10 @@
         <v>6</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
@@ -16580,7 +21125,7 @@
       <c r="Q130" s="8"/>
       <c r="R130" s="8"/>
       <c r="S130" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T130" s="8"/>
       <c r="U130" s="8"/>
@@ -16594,13 +21139,13 @@
       <c r="AC130" s="8"/>
       <c r="AD130" s="8"/>
       <c r="AE130" s="8" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AF130" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG130" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH130" s="8" t="s">
         <v>192</v>
@@ -16623,10 +21168,10 @@
         <v>6</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
@@ -16643,7 +21188,7 @@
       <c r="Q131" s="8"/>
       <c r="R131" s="8"/>
       <c r="S131" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T131" s="8"/>
       <c r="U131" s="8"/>
@@ -16657,13 +21202,13 @@
       <c r="AC131" s="8"/>
       <c r="AD131" s="8"/>
       <c r="AE131" s="8" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AF131" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG131" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH131" s="8" t="s">
         <v>192</v>
@@ -16686,10 +21231,10 @@
         <v>6</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
@@ -16706,7 +21251,7 @@
       <c r="Q132" s="8"/>
       <c r="R132" s="8"/>
       <c r="S132" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T132" s="8"/>
       <c r="U132" s="8"/>
@@ -16720,13 +21265,13 @@
       <c r="AC132" s="8"/>
       <c r="AD132" s="8"/>
       <c r="AE132" s="8" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AF132" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG132" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH132" s="8" t="s">
         <v>192</v>
@@ -16749,10 +21294,10 @@
         <v>6</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
@@ -16769,7 +21314,7 @@
       <c r="Q133" s="8"/>
       <c r="R133" s="8"/>
       <c r="S133" s="8" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="T133" s="8"/>
       <c r="U133" s="8"/>
@@ -16783,13 +21328,13 @@
       <c r="AC133" s="8"/>
       <c r="AD133" s="8"/>
       <c r="AE133" s="8" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AF133" s="8" t="s">
         <v>192</v>
       </c>
       <c r="AG133" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AH133" s="8" t="s">
         <v>192</v>
@@ -16809,12 +21354,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.71"/>
@@ -16857,7 +21402,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B4" s="5" t="str">
         <f aca="false">IF(COUNTIF(resultado_homogeneidad!$G:$G,"FALLA")&gt;0,"FALLA",IF(COUNTIF(resultado_homogeneidad!$G:$G,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
@@ -16891,7 +21436,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B7" s="5" t="str">
         <f aca="false">IF(COUNTIF(resultado_estabilidad!$G:$G,"FALLA")&gt;0,"FALLA",IF(COUNTIF(resultado_estabilidad!$G:$G,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
@@ -16925,7 +21470,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B10" s="5" t="str">
         <f aca="false">IF(COUNTIF(valor_asignado!$K:$K,"FALLA")&gt;0,"FALLA",IF(COUNTIF(valor_asignado!$K:$K,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
@@ -16948,7 +21493,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B12" s="5" t="str">
         <f aca="false">IF(COUNTIF(algoritmo_A!$E:$E,"FALLA")&gt;0,"FALLA",IF(COUNTIF(algoritmo_A!$E:$E,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
@@ -16960,113 +21505,137 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f aca="false">IF(COUNTIF(puntajes_EA!$N:$N,"FALLA")&gt;0,"FALLA",IF(COUNTIF(puntajes_EA!$N:$N,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f aca="false">IF(COUNTIF(informe_global!$R:$R,"FALLA")&gt;0,"FALLA",IF(COUNTIF(informe_global!$R:$R,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B14" s="5" t="str">
-        <f aca="false">IF(SUM(C20:C24)&gt;0,"FALLA","OK")</f>
+      <c r="B15" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f aca="false">IF(SUM(C22:C26)&gt;0,"FALLA","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>273</v>
-      </c>
-      <c r="B17" s="7" t="str">
-        <f aca="false">IF(COUNTIF(B2:B14,"FALLA")&gt;0,"FALLA",IF(COUNTIF(B2:B14,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
+      <c r="C16" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" s="7" t="str">
+        <f aca="false">IF(COUNTIF(B2:B16,"FALLA")&gt;0,"FALLA",IF(COUNTIF(B2:B16,"Pendiente")&gt;0,"PENDIENTE","OK"))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="2" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A20)+COUNTIF(resultado_estabilidad!$A:$G,A20)+COUNTIF(calc_homogeneidad!$A:$C,A20)+COUNTIF(calc_estabilidad!$A:$C,A20)+COUNTIF(valor_asignado!$A:$K,A20)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A20)+COUNTIF(algoritmo_A!$A:$E,A20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A21)+COUNTIF(resultado_estabilidad!$A:$G,A21)+COUNTIF(calc_homogeneidad!$A:$C,A21)+COUNTIF(calc_estabilidad!$A:$C,A21)+COUNTIF(valor_asignado!$A:$K,A21)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A21)+COUNTIF(algoritmo_A!$A:$E,A21)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C22" s="5" t="n">
-        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A22)+COUNTIF(resultado_estabilidad!$A:$G,A22)+COUNTIF(calc_homogeneidad!$A:$C,A22)+COUNTIF(calc_estabilidad!$A:$C,A22)+COUNTIF(valor_asignado!$A:$K,A22)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A22)+COUNTIF(algoritmo_A!$A:$E,A22)</f>
+        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A22)+COUNTIF(resultado_estabilidad!$A:$G,A22)+COUNTIF(calc_homogeneidad!$A:$C,A22)+COUNTIF(calc_estabilidad!$A:$C,A22)+COUNTIF(valor_asignado!$A:$K,A22)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A22)+COUNTIF(algoritmo_A!$A:$E,A22)+COUNTIF(puntajes_EA!$A:$N,A22)+COUNTIF(informe_global!$A:$R,A22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="C23" s="5" t="n">
-        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A23)+COUNTIF(resultado_estabilidad!$A:$G,A23)+COUNTIF(calc_homogeneidad!$A:$C,A23)+COUNTIF(calc_estabilidad!$A:$C,A23)+COUNTIF(valor_asignado!$A:$K,A23)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A23)+COUNTIF(algoritmo_A!$A:$E,A23)</f>
+        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A23)+COUNTIF(resultado_estabilidad!$A:$G,A23)+COUNTIF(calc_homogeneidad!$A:$C,A23)+COUNTIF(calc_estabilidad!$A:$C,A23)+COUNTIF(valor_asignado!$A:$K,A23)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A23)+COUNTIF(algoritmo_A!$A:$E,A23)+COUNTIF(puntajes_EA!$A:$N,A23)+COUNTIF(informe_global!$A:$R,A23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="5" t="n">
+        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A24)+COUNTIF(resultado_estabilidad!$A:$G,A24)+COUNTIF(calc_homogeneidad!$A:$C,A24)+COUNTIF(calc_estabilidad!$A:$C,A24)+COUNTIF(valor_asignado!$A:$K,A24)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A24)+COUNTIF(algoritmo_A!$A:$E,A24)+COUNTIF(puntajes_EA!$A:$N,A24)+COUNTIF(informe_global!$A:$R,A24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C24" s="5" t="n">
-        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A24)+COUNTIF(resultado_estabilidad!$A:$G,A24)+COUNTIF(calc_homogeneidad!$A:$C,A24)+COUNTIF(calc_estabilidad!$A:$C,A24)+COUNTIF(valor_asignado!$A:$K,A24)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A24)+COUNTIF(algoritmo_A!$A:$E,A24)</f>
+      <c r="B25" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A25)+COUNTIF(resultado_estabilidad!$A:$G,A25)+COUNTIF(calc_homogeneidad!$A:$C,A25)+COUNTIF(calc_estabilidad!$A:$C,A25)+COUNTIF(valor_asignado!$A:$K,A25)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A25)+COUNTIF(algoritmo_A!$A:$E,A25)+COUNTIF(puntajes_EA!$A:$N,A25)+COUNTIF(informe_global!$A:$R,A25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B26" s="7" t="n">
-        <f aca="false">SUM(C20:C24)</f>
+      <c r="B26" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <f aca="false">COUNTIF(resultado_homogeneidad!$A:$G,A26)+COUNTIF(resultado_estabilidad!$A:$G,A26)+COUNTIF(calc_homogeneidad!$A:$C,A26)+COUNTIF(calc_estabilidad!$A:$C,A26)+COUNTIF(valor_asignado!$A:$K,A26)+COUNTIF(algoritmo_A_iteraciones!$A:$Z,A26)+COUNTIF(algoritmo_A!$A:$E,A26)+COUNTIF(puntajes_EA!$A:$N,A26)+COUNTIF(informe_global!$A:$R,A26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <f aca="false">SUM(C22:C26)</f>
         <v>0</v>
       </c>
     </row>

--- a/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_0.xlsx
+++ b/validation_1/validation/excel/validacion_o3/formulas/validacion_formula_o3_0.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">Fecha de generacion</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-13 19:07:11 -0500</t>
+    <t xml:space="preserve">2026-05-13 19:17:29 -0500</t>
   </si>
   <si>
     <t xml:space="preserve">Script generador</t>
